--- a/app/download_dir/system_files/обувь_по коробам.xlsx
+++ b/app/download_dir/system_files/обувь_по коробам.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="1016">
   <si>
     <t xml:space="preserve">V_MANUFACTURER_CODE</t>
   </si>
@@ -369,144 +369,144 @@
     <t xml:space="preserve">Натуральная масляная кожа</t>
   </si>
   <si>
+    <t xml:space="preserve">Натуральная замша</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мужские</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сертификат</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АВСТРИЯ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БАЛЕТКИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЖЕВЫЙ/ЗЕЛЕНЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6403&gt; Обувь с подошвой из резины, пластмассы, натуральной или композиционной кожи и с верхом из натуральной кожи:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;CERT_EAC_18_TC&gt; Сертификат ЕАС '18 - вариант ТС</t>
+  </si>
+  <si>
     <t xml:space="preserve">Этиленвинилацетат</t>
   </si>
   <si>
-    <t xml:space="preserve">Мужские</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сертификат</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АВСТРИЯ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БАЛЕТКИ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЖЕВЫЙ/ЗЕЛЕНЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6403&gt; Обувь с подошвой из резины, пластмассы, натуральной или композиционной кожи и с верхом из натуральной кожи:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;CERT_EAC_18_TC&gt; Сертификат ЕАС '18 - вариант ТС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Натуральная замша</t>
+    <t xml:space="preserve">Унисекс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АЗЕРБАЙДЖАН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БАХИЛЫ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЖЕВЫЙ/СИНИЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6404&gt; Обувь с подошвой из резины, пластмассы, натуральной или композиционной кожи и с верхом из текстильных материалов:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;DECL_EAC&gt; Декларация EAC - вариант TC N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Велюр</t>
   </si>
   <si>
     <t xml:space="preserve">Термопластичная резина</t>
   </si>
   <si>
-    <t xml:space="preserve">Унисекс</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АЗЕРБАЙДЖАН</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БАХИЛЫ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЖЕВЫЙ/СИНИЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6404&gt; Обувь с подошвой из резины, пластмассы, натуральной или композиционной кожи и с верхом из текстильных материалов:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;DECL_EAC&gt; Декларация EAC - вариант TC N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Велюр</t>
+    <t xml:space="preserve">Детские</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АЛАНДСКИЕ ОСТРОВА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕРЦЫ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЛО-ЗЕЛЕНЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6405&gt; Обувь прочая:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;DECL_EAC_2&gt; Декларация EAC - вариант ЕАЭС N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ворсин</t>
   </si>
   <si>
     <t xml:space="preserve">Полимерный материал</t>
   </si>
   <si>
-    <t xml:space="preserve">Детские</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АЛАНДСКИЕ ОСТРОВА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕРЦЫ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЛО-ЗЕЛЕНЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6405&gt; Обувь прочая:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;DECL_EAC_2&gt; Декларация EAC - вариант ЕАЭС N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ворсин</t>
+    <t xml:space="preserve">Мальчик</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АЛБАНИЯ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОКСЕРКИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЛО-КОРИЧНЕВЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6401100000&gt; - обувь с защитным металлическим подноском</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;DECL_EAC_18_EAES&gt; Декларация ЕАС' 18 - вариант ЕАЭС N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нубук</t>
   </si>
   <si>
     <t xml:space="preserve">Резина</t>
   </si>
   <si>
-    <t xml:space="preserve">Мальчик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АЛБАНИЯ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОКСЕРКИ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЛО-КОРИЧНЕВЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6401100000&gt; - обувь с защитным металлическим подноском</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;DECL_EAC_18_EAES&gt; Декларация ЕАС' 18 - вариант ЕАЭС N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нубук</t>
+    <t xml:space="preserve">Девочка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АЛЖИР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОРЦОВКИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЛО-РОЗОВЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;640192&gt; - - закрывающая лодыжку, но не закрывающая колено:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;DECL_EAC_18_TC&gt; Декларация ЕАС '18 - вариант ТС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Спилок</t>
   </si>
   <si>
     <t xml:space="preserve">Пластмасса</t>
   </si>
   <si>
-    <t xml:space="preserve">Девочка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АЛЖИР</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОРЦОВКИ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЛО-РОЗОВЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;640192&gt; - - закрывающая лодыжку, но не закрывающая колено:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;DECL_EAC_18_TC&gt; Декларация ЕАС '18 - вариант ТС</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Спилок</t>
-  </si>
-  <si>
     <t xml:space="preserve">АМЕРИКАНСКИЕ ВИРГИНСКИЕ ОСТРОВА</t>
   </si>
   <si>
@@ -525,118 +525,118 @@
     <t xml:space="preserve">Натуральный мех</t>
   </si>
   <si>
+    <t xml:space="preserve">АМЕРИКАНСКОЕ САМОА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОТИЛЬОНЫ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6401929000&gt; --- с верхом из пластмассы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;FIRE_SAFETY_18&gt; Сертификат ТР РФ  о пожарной безопасности '18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Юфть</t>
+  </si>
+  <si>
     <t xml:space="preserve">Полиуретан</t>
   </si>
   <si>
-    <t xml:space="preserve">АМЕРИКАНСКОЕ САМОА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОТИЛЬОНЫ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6401929000&gt; --- с верхом из пластмассы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;FIRE_SAFETY_18&gt; Сертификат ТР РФ  о пожарной безопасности '18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Юфть</t>
+    <t xml:space="preserve">АНГИЛЬЯ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЛЫЙ/СЕРЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6401990000&gt; - - прочая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;FIRE_SAFETY_DECL&gt; Декларация ТР РФ  о пожарной безопасности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Композиционная кожа</t>
   </si>
   <si>
     <t xml:space="preserve">Поливинилхлорид</t>
   </si>
   <si>
-    <t xml:space="preserve">АНГИЛЬЯ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЛЫЙ/СЕРЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6401990000&gt; - - прочая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;FIRE_SAFETY_DECL&gt; Декларация ТР РФ  о пожарной безопасности</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Композиционная кожа</t>
+    <t xml:space="preserve">АНГОЛА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОТИНКИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БЕЛЫЙ/СИНИЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;640192&gt;  - прочая обувь: -- закрывающая лодыжку, но не закрывающая колено:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;FIRE_SAFETY_DECL_18&gt; Декларация ТР РФ  о пожарной безопасности '18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Экокожа</t>
   </si>
   <si>
     <t xml:space="preserve">Пробка</t>
   </si>
   <si>
-    <t xml:space="preserve">АНГОЛА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОТИНКИ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БЕЛЫЙ/СИНИЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;640192&gt;  - прочая обувь: -- закрывающая лодыжку, но не закрывающая колено:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;FIRE_SAFETY_DECL_18&gt; Декларация ТР РФ  о пожарной безопасности '18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Экокожа</t>
+    <t xml:space="preserve">АНДОРРА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОТИНКИ ВЫСОКИЕ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БИРЮЗОВЫЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6401990000&gt;  - прочая обувь: -- прочая</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;CERT_GOST_R&gt; Сертификат ГОСТ Р</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Искусственная кожа</t>
   </si>
   <si>
     <t xml:space="preserve">Войлок</t>
   </si>
   <si>
-    <t xml:space="preserve">АНДОРРА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОТИНКИ ВЫСОКИЕ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БИРЮЗОВЫЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6401990000&gt;  - прочая обувь: -- прочая</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;CERT_GOST_R&gt; Сертификат ГОСТ Р</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Искусственная кожа</t>
+    <t xml:space="preserve">АНТАРКТИДА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОТИНКИ ДЛЯ БАСКЕТБОЛА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">БОРДОВО-РЫЖИЙ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;6402200000&gt; - обувь с верхом из ремешков или полосок, прикрепленных к подошве заклепками</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;CERT_GOST_R_18&gt; Сертификат ГОСТ Р '18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Искусственная шерсть</t>
   </si>
   <si>
     <t xml:space="preserve">Пенополиуретан</t>
-  </si>
-  <si>
-    <t xml:space="preserve">АНТАРКТИДА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОТИНКИ ДЛЯ БАСКЕТБОЛА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">БОРДОВО-РЫЖИЙ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;6402200000&gt; - обувь с верхом из ремешков или полосок, прикрепленных к подошве заклепками</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;CERT_GOST_R_18&gt; Сертификат ГОСТ Р '18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Искусственная шерсть</t>
   </si>
   <si>
     <t xml:space="preserve">АНТИГУА И БАРБУДА</t>
@@ -32495,6 +32495,7 @@
       <c r="D1475" s="62"/>
       <c r="E1475" s="63"/>
       <c r="F1475" s="63"/>
+      <c r="G1475" s="63"/>
       <c r="H1475" s="63"/>
       <c r="I1475" s="64" t="n">
         <f aca="false">J1475*K1475</f>
@@ -32510,6 +32511,7 @@
       <c r="D1476" s="62"/>
       <c r="E1476" s="63"/>
       <c r="F1476" s="63"/>
+      <c r="G1476" s="63"/>
       <c r="H1476" s="63"/>
       <c r="I1476" s="64" t="n">
         <f aca="false">J1476*K1476</f>
@@ -32525,6 +32527,7 @@
       <c r="D1477" s="62"/>
       <c r="E1477" s="63"/>
       <c r="F1477" s="63"/>
+      <c r="G1477" s="63"/>
       <c r="H1477" s="63"/>
       <c r="I1477" s="64" t="n">
         <f aca="false">J1477*K1477</f>
@@ -32540,6 +32543,7 @@
       <c r="D1478" s="62"/>
       <c r="E1478" s="63"/>
       <c r="F1478" s="63"/>
+      <c r="G1478" s="63"/>
       <c r="H1478" s="63"/>
       <c r="I1478" s="64" t="n">
         <f aca="false">J1478*K1478</f>
@@ -32555,6 +32559,7 @@
       <c r="D1479" s="62"/>
       <c r="E1479" s="63"/>
       <c r="F1479" s="63"/>
+      <c r="G1479" s="63"/>
       <c r="H1479" s="63"/>
       <c r="I1479" s="64" t="n">
         <f aca="false">J1479*K1479</f>
@@ -32570,6 +32575,7 @@
       <c r="D1480" s="62"/>
       <c r="E1480" s="63"/>
       <c r="F1480" s="63"/>
+      <c r="G1480" s="63"/>
       <c r="H1480" s="63"/>
       <c r="I1480" s="64" t="n">
         <f aca="false">J1480*K1480</f>
@@ -32585,6 +32591,7 @@
       <c r="D1481" s="62"/>
       <c r="E1481" s="63"/>
       <c r="F1481" s="63"/>
+      <c r="G1481" s="63"/>
       <c r="H1481" s="63"/>
       <c r="I1481" s="64" t="n">
         <f aca="false">J1481*K1481</f>
@@ -32600,6 +32607,7 @@
       <c r="D1482" s="62"/>
       <c r="E1482" s="63"/>
       <c r="F1482" s="63"/>
+      <c r="G1482" s="63"/>
       <c r="H1482" s="63"/>
       <c r="I1482" s="64" t="n">
         <f aca="false">J1482*K1482</f>
@@ -32615,6 +32623,7 @@
       <c r="D1483" s="62"/>
       <c r="E1483" s="63"/>
       <c r="F1483" s="63"/>
+      <c r="G1483" s="63"/>
       <c r="H1483" s="63"/>
       <c r="I1483" s="64" t="n">
         <f aca="false">J1483*K1483</f>
@@ -32630,6 +32639,7 @@
       <c r="D1484" s="62"/>
       <c r="E1484" s="63"/>
       <c r="F1484" s="63"/>
+      <c r="G1484" s="63"/>
       <c r="H1484" s="63"/>
       <c r="I1484" s="64" t="n">
         <f aca="false">J1484*K1484</f>
@@ -32645,6 +32655,7 @@
       <c r="D1485" s="62"/>
       <c r="E1485" s="63"/>
       <c r="F1485" s="63"/>
+      <c r="G1485" s="63"/>
       <c r="H1485" s="63"/>
       <c r="I1485" s="64" t="n">
         <f aca="false">J1485*K1485</f>
@@ -32660,6 +32671,7 @@
       <c r="D1486" s="62"/>
       <c r="E1486" s="63"/>
       <c r="F1486" s="63"/>
+      <c r="G1486" s="63"/>
       <c r="H1486" s="63"/>
       <c r="I1486" s="64" t="n">
         <f aca="false">J1486*K1486</f>
@@ -32675,6 +32687,7 @@
       <c r="D1487" s="62"/>
       <c r="E1487" s="63"/>
       <c r="F1487" s="63"/>
+      <c r="G1487" s="63"/>
       <c r="H1487" s="63"/>
       <c r="I1487" s="64" t="n">
         <f aca="false">J1487*K1487</f>
@@ -32690,6 +32703,7 @@
       <c r="D1488" s="62"/>
       <c r="E1488" s="63"/>
       <c r="F1488" s="63"/>
+      <c r="G1488" s="63"/>
       <c r="H1488" s="63"/>
       <c r="I1488" s="64" t="n">
         <f aca="false">J1488*K1488</f>
@@ -32705,6 +32719,7 @@
       <c r="D1489" s="62"/>
       <c r="E1489" s="63"/>
       <c r="F1489" s="63"/>
+      <c r="G1489" s="63"/>
       <c r="H1489" s="63"/>
       <c r="I1489" s="64" t="n">
         <f aca="false">J1489*K1489</f>
@@ -32720,6 +32735,7 @@
       <c r="D1490" s="62"/>
       <c r="E1490" s="63"/>
       <c r="F1490" s="63"/>
+      <c r="G1490" s="63"/>
       <c r="H1490" s="63"/>
       <c r="I1490" s="64" t="n">
         <f aca="false">J1490*K1490</f>
@@ -32735,6 +32751,7 @@
       <c r="D1491" s="62"/>
       <c r="E1491" s="63"/>
       <c r="F1491" s="63"/>
+      <c r="G1491" s="63"/>
       <c r="H1491" s="63"/>
       <c r="I1491" s="64" t="n">
         <f aca="false">J1491*K1491</f>
@@ -32750,6 +32767,7 @@
       <c r="D1492" s="62"/>
       <c r="E1492" s="63"/>
       <c r="F1492" s="63"/>
+      <c r="G1492" s="63"/>
       <c r="H1492" s="63"/>
       <c r="I1492" s="64" t="n">
         <f aca="false">J1492*K1492</f>
@@ -32765,6 +32783,7 @@
       <c r="D1493" s="62"/>
       <c r="E1493" s="63"/>
       <c r="F1493" s="63"/>
+      <c r="G1493" s="63"/>
       <c r="H1493" s="63"/>
       <c r="I1493" s="64" t="n">
         <f aca="false">J1493*K1493</f>
@@ -32780,6 +32799,7 @@
       <c r="D1494" s="62"/>
       <c r="E1494" s="63"/>
       <c r="F1494" s="63"/>
+      <c r="G1494" s="63"/>
       <c r="H1494" s="63"/>
       <c r="I1494" s="64" t="n">
         <f aca="false">J1494*K1494</f>
@@ -32795,6 +32815,7 @@
       <c r="D1495" s="62"/>
       <c r="E1495" s="63"/>
       <c r="F1495" s="63"/>
+      <c r="G1495" s="63"/>
       <c r="H1495" s="63"/>
       <c r="I1495" s="64" t="n">
         <f aca="false">J1495*K1495</f>
@@ -32810,6 +32831,7 @@
       <c r="D1496" s="62"/>
       <c r="E1496" s="63"/>
       <c r="F1496" s="63"/>
+      <c r="G1496" s="63"/>
       <c r="H1496" s="63"/>
       <c r="I1496" s="64" t="n">
         <f aca="false">J1496*K1496</f>
@@ -32825,6 +32847,7 @@
       <c r="D1497" s="62"/>
       <c r="E1497" s="63"/>
       <c r="F1497" s="63"/>
+      <c r="G1497" s="63"/>
       <c r="H1497" s="63"/>
       <c r="I1497" s="64" t="n">
         <f aca="false">J1497*K1497</f>
@@ -32840,6 +32863,7 @@
       <c r="D1498" s="62"/>
       <c r="E1498" s="63"/>
       <c r="F1498" s="63"/>
+      <c r="G1498" s="63"/>
       <c r="H1498" s="63"/>
       <c r="I1498" s="64" t="n">
         <f aca="false">J1498*K1498</f>
@@ -32855,6 +32879,7 @@
       <c r="D1499" s="62"/>
       <c r="E1499" s="63"/>
       <c r="F1499" s="63"/>
+      <c r="G1499" s="63"/>
       <c r="H1499" s="63"/>
       <c r="I1499" s="64" t="n">
         <f aca="false">J1499*K1499</f>
@@ -32870,6 +32895,7 @@
       <c r="D1500" s="62"/>
       <c r="E1500" s="63"/>
       <c r="F1500" s="63"/>
+      <c r="G1500" s="63"/>
       <c r="H1500" s="63"/>
       <c r="I1500" s="64" t="n">
         <f aca="false">J1500*K1500</f>
@@ -32885,6 +32911,7 @@
       <c r="D1501" s="62"/>
       <c r="E1501" s="63"/>
       <c r="F1501" s="63"/>
+      <c r="G1501" s="63"/>
       <c r="H1501" s="63"/>
       <c r="I1501" s="64" t="n">
         <f aca="false">J1501*K1501</f>
@@ -32900,6 +32927,7 @@
       <c r="D1502" s="62"/>
       <c r="E1502" s="63"/>
       <c r="F1502" s="63"/>
+      <c r="G1502" s="63"/>
       <c r="H1502" s="63"/>
       <c r="I1502" s="64" t="n">
         <f aca="false">J1502*K1502</f>
@@ -32915,6 +32943,7 @@
       <c r="D1503" s="62"/>
       <c r="E1503" s="63"/>
       <c r="F1503" s="63"/>
+      <c r="G1503" s="63"/>
       <c r="H1503" s="63"/>
       <c r="I1503" s="64" t="n">
         <f aca="false">J1503*K1503</f>
@@ -32930,6 +32959,7 @@
       <c r="D1504" s="62"/>
       <c r="E1504" s="63"/>
       <c r="F1504" s="63"/>
+      <c r="G1504" s="63"/>
       <c r="H1504" s="63"/>
       <c r="I1504" s="64" t="n">
         <f aca="false">J1504*K1504</f>
@@ -32945,6 +32975,7 @@
       <c r="D1505" s="62"/>
       <c r="E1505" s="63"/>
       <c r="F1505" s="63"/>
+      <c r="G1505" s="63"/>
       <c r="H1505" s="63"/>
       <c r="I1505" s="64" t="n">
         <f aca="false">J1505*K1505</f>
@@ -32960,6 +32991,7 @@
       <c r="D1506" s="62"/>
       <c r="E1506" s="63"/>
       <c r="F1506" s="63"/>
+      <c r="G1506" s="63"/>
       <c r="H1506" s="63"/>
       <c r="I1506" s="64" t="n">
         <f aca="false">J1506*K1506</f>
@@ -32975,6 +33007,7 @@
       <c r="D1507" s="62"/>
       <c r="E1507" s="63"/>
       <c r="F1507" s="63"/>
+      <c r="G1507" s="63"/>
       <c r="H1507" s="63"/>
       <c r="I1507" s="64" t="n">
         <f aca="false">J1507*K1507</f>
@@ -32990,6 +33023,7 @@
       <c r="D1508" s="62"/>
       <c r="E1508" s="63"/>
       <c r="F1508" s="63"/>
+      <c r="G1508" s="63"/>
       <c r="H1508" s="63"/>
       <c r="I1508" s="64" t="n">
         <f aca="false">J1508*K1508</f>
@@ -33005,6 +33039,7 @@
       <c r="D1509" s="62"/>
       <c r="E1509" s="63"/>
       <c r="F1509" s="63"/>
+      <c r="G1509" s="63"/>
       <c r="H1509" s="63"/>
       <c r="I1509" s="64" t="n">
         <f aca="false">J1509*K1509</f>
@@ -33020,6 +33055,7 @@
       <c r="D1510" s="62"/>
       <c r="E1510" s="63"/>
       <c r="F1510" s="63"/>
+      <c r="G1510" s="63"/>
       <c r="H1510" s="63"/>
       <c r="I1510" s="64" t="n">
         <f aca="false">J1510*K1510</f>
@@ -33035,6 +33071,7 @@
       <c r="D1511" s="62"/>
       <c r="E1511" s="63"/>
       <c r="F1511" s="63"/>
+      <c r="G1511" s="63"/>
       <c r="H1511" s="63"/>
       <c r="I1511" s="64" t="n">
         <f aca="false">J1511*K1511</f>
@@ -33050,6 +33087,7 @@
       <c r="D1512" s="62"/>
       <c r="E1512" s="63"/>
       <c r="F1512" s="63"/>
+      <c r="G1512" s="63"/>
       <c r="H1512" s="63"/>
       <c r="I1512" s="64" t="n">
         <f aca="false">J1512*K1512</f>
@@ -33065,6 +33103,7 @@
       <c r="D1513" s="62"/>
       <c r="E1513" s="63"/>
       <c r="F1513" s="63"/>
+      <c r="G1513" s="63"/>
       <c r="H1513" s="63"/>
       <c r="I1513" s="64" t="n">
         <f aca="false">J1513*K1513</f>
@@ -33080,6 +33119,7 @@
       <c r="D1514" s="62"/>
       <c r="E1514" s="63"/>
       <c r="F1514" s="63"/>
+      <c r="G1514" s="63"/>
       <c r="H1514" s="63"/>
       <c r="I1514" s="64" t="n">
         <f aca="false">J1514*K1514</f>
@@ -33095,6 +33135,7 @@
       <c r="D1515" s="62"/>
       <c r="E1515" s="63"/>
       <c r="F1515" s="63"/>
+      <c r="G1515" s="63"/>
       <c r="H1515" s="63"/>
       <c r="I1515" s="64" t="n">
         <f aca="false">J1515*K1515</f>
@@ -33110,6 +33151,7 @@
       <c r="D1516" s="62"/>
       <c r="E1516" s="63"/>
       <c r="F1516" s="63"/>
+      <c r="G1516" s="63"/>
       <c r="H1516" s="63"/>
       <c r="I1516" s="64" t="n">
         <f aca="false">J1516*K1516</f>
@@ -33125,6 +33167,7 @@
       <c r="D1517" s="62"/>
       <c r="E1517" s="63"/>
       <c r="F1517" s="63"/>
+      <c r="G1517" s="63"/>
       <c r="H1517" s="63"/>
       <c r="I1517" s="64" t="n">
         <f aca="false">J1517*K1517</f>
@@ -33140,6 +33183,7 @@
       <c r="D1518" s="62"/>
       <c r="E1518" s="63"/>
       <c r="F1518" s="63"/>
+      <c r="G1518" s="63"/>
       <c r="H1518" s="63"/>
       <c r="I1518" s="64" t="n">
         <f aca="false">J1518*K1518</f>
@@ -33155,6 +33199,7 @@
       <c r="D1519" s="62"/>
       <c r="E1519" s="63"/>
       <c r="F1519" s="63"/>
+      <c r="G1519" s="63"/>
       <c r="H1519" s="63"/>
       <c r="I1519" s="64" t="n">
         <f aca="false">J1519*K1519</f>
@@ -33170,6 +33215,7 @@
       <c r="D1520" s="62"/>
       <c r="E1520" s="63"/>
       <c r="F1520" s="63"/>
+      <c r="G1520" s="63"/>
       <c r="H1520" s="63"/>
       <c r="I1520" s="64" t="n">
         <f aca="false">J1520*K1520</f>
@@ -33185,6 +33231,7 @@
       <c r="D1521" s="62"/>
       <c r="E1521" s="63"/>
       <c r="F1521" s="63"/>
+      <c r="G1521" s="63"/>
       <c r="H1521" s="63"/>
       <c r="I1521" s="64" t="n">
         <f aca="false">J1521*K1521</f>
@@ -33200,6 +33247,7 @@
       <c r="D1522" s="62"/>
       <c r="E1522" s="63"/>
       <c r="F1522" s="63"/>
+      <c r="G1522" s="63"/>
       <c r="H1522" s="63"/>
       <c r="I1522" s="64" t="n">
         <f aca="false">J1522*K1522</f>
@@ -33215,6 +33263,7 @@
       <c r="D1523" s="62"/>
       <c r="E1523" s="63"/>
       <c r="F1523" s="63"/>
+      <c r="G1523" s="63"/>
       <c r="H1523" s="63"/>
       <c r="I1523" s="64" t="n">
         <f aca="false">J1523*K1523</f>
@@ -33230,6 +33279,7 @@
       <c r="D1524" s="62"/>
       <c r="E1524" s="63"/>
       <c r="F1524" s="63"/>
+      <c r="G1524" s="63"/>
       <c r="H1524" s="63"/>
       <c r="I1524" s="64" t="n">
         <f aca="false">J1524*K1524</f>
@@ -33245,6 +33295,7 @@
       <c r="D1525" s="62"/>
       <c r="E1525" s="63"/>
       <c r="F1525" s="63"/>
+      <c r="G1525" s="63"/>
       <c r="H1525" s="63"/>
       <c r="I1525" s="64" t="n">
         <f aca="false">J1525*K1525</f>
@@ -33260,6 +33311,7 @@
       <c r="D1526" s="62"/>
       <c r="E1526" s="63"/>
       <c r="F1526" s="63"/>
+      <c r="G1526" s="63"/>
       <c r="H1526" s="63"/>
       <c r="I1526" s="64" t="n">
         <f aca="false">J1526*K1526</f>
@@ -33275,6 +33327,7 @@
       <c r="D1527" s="62"/>
       <c r="E1527" s="63"/>
       <c r="F1527" s="63"/>
+      <c r="G1527" s="63"/>
       <c r="H1527" s="63"/>
       <c r="I1527" s="64" t="n">
         <f aca="false">J1527*K1527</f>
@@ -33290,6 +33343,7 @@
       <c r="D1528" s="62"/>
       <c r="E1528" s="63"/>
       <c r="F1528" s="63"/>
+      <c r="G1528" s="63"/>
       <c r="H1528" s="63"/>
       <c r="I1528" s="64" t="n">
         <f aca="false">J1528*K1528</f>
@@ -33305,6 +33359,7 @@
       <c r="D1529" s="62"/>
       <c r="E1529" s="63"/>
       <c r="F1529" s="63"/>
+      <c r="G1529" s="63"/>
       <c r="H1529" s="63"/>
       <c r="I1529" s="64" t="n">
         <f aca="false">J1529*K1529</f>
@@ -33320,6 +33375,7 @@
       <c r="D1530" s="62"/>
       <c r="E1530" s="63"/>
       <c r="F1530" s="63"/>
+      <c r="G1530" s="63"/>
       <c r="H1530" s="63"/>
       <c r="I1530" s="64" t="n">
         <f aca="false">J1530*K1530</f>
@@ -33335,6 +33391,7 @@
       <c r="D1531" s="62"/>
       <c r="E1531" s="63"/>
       <c r="F1531" s="63"/>
+      <c r="G1531" s="63"/>
       <c r="H1531" s="63"/>
       <c r="I1531" s="64" t="n">
         <f aca="false">J1531*K1531</f>
@@ -33350,6 +33407,7 @@
       <c r="D1532" s="62"/>
       <c r="E1532" s="63"/>
       <c r="F1532" s="63"/>
+      <c r="G1532" s="63"/>
       <c r="H1532" s="63"/>
       <c r="I1532" s="64" t="n">
         <f aca="false">J1532*K1532</f>
@@ -33365,6 +33423,7 @@
       <c r="D1533" s="62"/>
       <c r="E1533" s="63"/>
       <c r="F1533" s="63"/>
+      <c r="G1533" s="63"/>
       <c r="H1533" s="63"/>
       <c r="I1533" s="64" t="n">
         <f aca="false">J1533*K1533</f>
@@ -33380,6 +33439,7 @@
       <c r="D1534" s="62"/>
       <c r="E1534" s="63"/>
       <c r="F1534" s="63"/>
+      <c r="G1534" s="63"/>
       <c r="H1534" s="63"/>
       <c r="I1534" s="64" t="n">
         <f aca="false">J1534*K1534</f>
@@ -33395,6 +33455,7 @@
       <c r="D1535" s="62"/>
       <c r="E1535" s="63"/>
       <c r="F1535" s="63"/>
+      <c r="G1535" s="63"/>
       <c r="H1535" s="63"/>
       <c r="I1535" s="64" t="n">
         <f aca="false">J1535*K1535</f>
@@ -33410,6 +33471,7 @@
       <c r="D1536" s="62"/>
       <c r="E1536" s="63"/>
       <c r="F1536" s="63"/>
+      <c r="G1536" s="63"/>
       <c r="H1536" s="63"/>
       <c r="I1536" s="64" t="n">
         <f aca="false">J1536*K1536</f>
@@ -33425,6 +33487,7 @@
       <c r="D1537" s="62"/>
       <c r="E1537" s="63"/>
       <c r="F1537" s="63"/>
+      <c r="G1537" s="63"/>
       <c r="H1537" s="63"/>
       <c r="I1537" s="64" t="n">
         <f aca="false">J1537*K1537</f>
@@ -33440,6 +33503,7 @@
       <c r="D1538" s="62"/>
       <c r="E1538" s="63"/>
       <c r="F1538" s="63"/>
+      <c r="G1538" s="63"/>
       <c r="H1538" s="63"/>
       <c r="I1538" s="64" t="n">
         <f aca="false">J1538*K1538</f>
@@ -33455,6 +33519,7 @@
       <c r="D1539" s="62"/>
       <c r="E1539" s="63"/>
       <c r="F1539" s="63"/>
+      <c r="G1539" s="63"/>
       <c r="H1539" s="63"/>
       <c r="I1539" s="64" t="n">
         <f aca="false">J1539*K1539</f>
@@ -33470,6 +33535,7 @@
       <c r="D1540" s="62"/>
       <c r="E1540" s="63"/>
       <c r="F1540" s="63"/>
+      <c r="G1540" s="63"/>
       <c r="H1540" s="63"/>
       <c r="I1540" s="64" t="n">
         <f aca="false">J1540*K1540</f>
@@ -33484,6 +33550,7 @@
     <row r="1541" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1541" s="62"/>
       <c r="E1541" s="63"/>
+      <c r="G1541" s="63"/>
       <c r="H1541" s="63"/>
       <c r="I1541" s="64" t="n">
         <f aca="false">J1541*K1541</f>
@@ -33498,6 +33565,7 @@
     <row r="1542" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1542" s="62"/>
       <c r="E1542" s="63"/>
+      <c r="G1542" s="63"/>
       <c r="H1542" s="63"/>
       <c r="I1542" s="64" t="n">
         <f aca="false">J1542*K1542</f>
@@ -33512,6 +33580,7 @@
     <row r="1543" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1543" s="62"/>
       <c r="E1543" s="63"/>
+      <c r="G1543" s="63"/>
       <c r="H1543" s="63"/>
       <c r="I1543" s="64" t="n">
         <f aca="false">J1543*K1543</f>
@@ -33526,6 +33595,7 @@
     <row r="1544" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1544" s="62"/>
       <c r="E1544" s="63"/>
+      <c r="G1544" s="63"/>
       <c r="H1544" s="63"/>
       <c r="I1544" s="64" t="n">
         <f aca="false">J1544*K1544</f>
@@ -33540,6 +33610,7 @@
     <row r="1545" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1545" s="62"/>
       <c r="E1545" s="63"/>
+      <c r="G1545" s="63"/>
       <c r="H1545" s="63"/>
       <c r="I1545" s="64" t="n">
         <f aca="false">J1545*K1545</f>
@@ -33554,6 +33625,7 @@
     <row r="1546" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1546" s="62"/>
       <c r="E1546" s="63"/>
+      <c r="G1546" s="63"/>
       <c r="H1546" s="63"/>
       <c r="I1546" s="64" t="n">
         <f aca="false">J1546*K1546</f>
@@ -33568,6 +33640,7 @@
     <row r="1547" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1547" s="62"/>
       <c r="E1547" s="63"/>
+      <c r="G1547" s="63"/>
       <c r="H1547" s="63"/>
       <c r="I1547" s="64" t="n">
         <f aca="false">J1547*K1547</f>
@@ -33582,6 +33655,7 @@
     <row r="1548" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1548" s="62"/>
       <c r="E1548" s="63"/>
+      <c r="G1548" s="63"/>
       <c r="H1548" s="63"/>
       <c r="I1548" s="64" t="n">
         <f aca="false">J1548*K1548</f>
@@ -33596,6 +33670,7 @@
     <row r="1549" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1549" s="62"/>
       <c r="E1549" s="63"/>
+      <c r="G1549" s="63"/>
       <c r="H1549" s="63"/>
       <c r="I1549" s="64" t="n">
         <f aca="false">J1549*K1549</f>
@@ -33610,6 +33685,7 @@
     <row r="1550" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1550" s="62"/>
       <c r="E1550" s="63"/>
+      <c r="G1550" s="63"/>
       <c r="H1550" s="63"/>
       <c r="I1550" s="64" t="n">
         <f aca="false">J1550*K1550</f>
@@ -33624,6 +33700,7 @@
     <row r="1551" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1551" s="62"/>
       <c r="E1551" s="63"/>
+      <c r="G1551" s="63"/>
       <c r="H1551" s="63"/>
       <c r="I1551" s="64" t="n">
         <f aca="false">J1551*K1551</f>
@@ -33638,6 +33715,7 @@
     <row r="1552" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1552" s="62"/>
       <c r="E1552" s="63"/>
+      <c r="G1552" s="63"/>
       <c r="H1552" s="63"/>
       <c r="I1552" s="64" t="n">
         <f aca="false">J1552*K1552</f>
@@ -33652,6 +33730,7 @@
     <row r="1553" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1553" s="62"/>
       <c r="E1553" s="63"/>
+      <c r="G1553" s="63"/>
       <c r="H1553" s="63"/>
       <c r="I1553" s="64" t="n">
         <f aca="false">J1553*K1553</f>
@@ -33666,6 +33745,7 @@
     <row r="1554" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1554" s="62"/>
       <c r="E1554" s="63"/>
+      <c r="G1554" s="63"/>
       <c r="H1554" s="63"/>
       <c r="I1554" s="64" t="n">
         <f aca="false">J1554*K1554</f>
@@ -33680,6 +33760,7 @@
     <row r="1555" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1555" s="62"/>
       <c r="E1555" s="63"/>
+      <c r="G1555" s="63"/>
       <c r="H1555" s="63"/>
       <c r="I1555" s="64" t="n">
         <f aca="false">J1555*K1555</f>
@@ -33694,6 +33775,7 @@
     <row r="1556" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1556" s="62"/>
       <c r="E1556" s="63"/>
+      <c r="G1556" s="63"/>
       <c r="H1556" s="63"/>
       <c r="I1556" s="64" t="n">
         <f aca="false">J1556*K1556</f>
@@ -33708,6 +33790,7 @@
     <row r="1557" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1557" s="62"/>
       <c r="E1557" s="63"/>
+      <c r="G1557" s="63"/>
       <c r="H1557" s="63"/>
       <c r="I1557" s="64" t="n">
         <f aca="false">J1557*K1557</f>
@@ -33722,6 +33805,7 @@
     <row r="1558" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1558" s="62"/>
       <c r="E1558" s="63"/>
+      <c r="G1558" s="63"/>
       <c r="H1558" s="63"/>
       <c r="I1558" s="64" t="n">
         <f aca="false">J1558*K1558</f>
@@ -33736,6 +33820,7 @@
     <row r="1559" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1559" s="62"/>
       <c r="E1559" s="63"/>
+      <c r="G1559" s="63"/>
       <c r="H1559" s="63"/>
       <c r="I1559" s="64" t="n">
         <f aca="false">J1559*K1559</f>
@@ -33750,6 +33835,7 @@
     <row r="1560" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1560" s="62"/>
       <c r="E1560" s="63"/>
+      <c r="G1560" s="63"/>
       <c r="H1560" s="63"/>
       <c r="I1560" s="64" t="n">
         <f aca="false">J1560*K1560</f>
@@ -33764,6 +33850,7 @@
     <row r="1561" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1561" s="62"/>
       <c r="E1561" s="63"/>
+      <c r="G1561" s="63"/>
       <c r="H1561" s="63"/>
       <c r="I1561" s="64" t="n">
         <f aca="false">J1561*K1561</f>
@@ -33778,6 +33865,7 @@
     <row r="1562" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1562" s="62"/>
       <c r="E1562" s="63"/>
+      <c r="G1562" s="63"/>
       <c r="H1562" s="63"/>
       <c r="I1562" s="64" t="n">
         <f aca="false">J1562*K1562</f>
@@ -33792,6 +33880,7 @@
     <row r="1563" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1563" s="62"/>
       <c r="E1563" s="63"/>
+      <c r="G1563" s="63"/>
       <c r="H1563" s="63"/>
       <c r="I1563" s="64" t="n">
         <f aca="false">J1563*K1563</f>
@@ -33806,6 +33895,7 @@
     <row r="1564" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1564" s="62"/>
       <c r="E1564" s="63"/>
+      <c r="G1564" s="63"/>
       <c r="H1564" s="63"/>
       <c r="I1564" s="64" t="n">
         <f aca="false">J1564*K1564</f>
@@ -33820,6 +33910,7 @@
     <row r="1565" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1565" s="62"/>
       <c r="E1565" s="63"/>
+      <c r="G1565" s="63"/>
       <c r="H1565" s="63"/>
       <c r="I1565" s="64" t="n">
         <f aca="false">J1565*K1565</f>
@@ -33834,6 +33925,7 @@
     <row r="1566" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1566" s="62"/>
       <c r="E1566" s="63"/>
+      <c r="G1566" s="63"/>
       <c r="H1566" s="63"/>
       <c r="I1566" s="64" t="n">
         <f aca="false">J1566*K1566</f>
@@ -33848,6 +33940,7 @@
     <row r="1567" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1567" s="62"/>
       <c r="E1567" s="63"/>
+      <c r="G1567" s="63"/>
       <c r="H1567" s="63"/>
       <c r="I1567" s="64" t="n">
         <f aca="false">J1567*K1567</f>
@@ -33862,6 +33955,7 @@
     <row r="1568" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1568" s="62"/>
       <c r="E1568" s="63"/>
+      <c r="G1568" s="63"/>
       <c r="H1568" s="63"/>
       <c r="I1568" s="64" t="n">
         <f aca="false">J1568*K1568</f>
@@ -33876,6 +33970,7 @@
     <row r="1569" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1569" s="62"/>
       <c r="E1569" s="63"/>
+      <c r="G1569" s="63"/>
       <c r="H1569" s="63"/>
       <c r="I1569" s="64" t="n">
         <f aca="false">J1569*K1569</f>
@@ -33890,6 +33985,7 @@
     <row r="1570" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1570" s="62"/>
       <c r="E1570" s="63"/>
+      <c r="G1570" s="63"/>
       <c r="H1570" s="63"/>
       <c r="I1570" s="64" t="n">
         <f aca="false">J1570*K1570</f>
@@ -33904,6 +34000,7 @@
     <row r="1571" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1571" s="62"/>
       <c r="E1571" s="63"/>
+      <c r="G1571" s="63"/>
       <c r="H1571" s="63"/>
       <c r="I1571" s="64" t="n">
         <f aca="false">J1571*K1571</f>
@@ -33918,6 +34015,7 @@
     <row r="1572" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1572" s="62"/>
       <c r="E1572" s="63"/>
+      <c r="G1572" s="63"/>
       <c r="H1572" s="63"/>
       <c r="I1572" s="64" t="n">
         <f aca="false">J1572*K1572</f>
@@ -33932,6 +34030,7 @@
     <row r="1573" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1573" s="62"/>
       <c r="E1573" s="63"/>
+      <c r="G1573" s="63"/>
       <c r="H1573" s="63"/>
       <c r="I1573" s="64" t="n">
         <f aca="false">J1573*K1573</f>
@@ -33946,6 +34045,7 @@
     <row r="1574" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1574" s="62"/>
       <c r="E1574" s="63"/>
+      <c r="G1574" s="63"/>
       <c r="H1574" s="63"/>
       <c r="I1574" s="64" t="n">
         <f aca="false">J1574*K1574</f>
@@ -33960,6 +34060,7 @@
     <row r="1575" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1575" s="62"/>
       <c r="E1575" s="63"/>
+      <c r="G1575" s="63"/>
       <c r="H1575" s="63"/>
       <c r="I1575" s="64" t="n">
         <f aca="false">J1575*K1575</f>
@@ -33974,6 +34075,7 @@
     <row r="1576" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1576" s="62"/>
       <c r="E1576" s="63"/>
+      <c r="G1576" s="63"/>
       <c r="H1576" s="63"/>
       <c r="I1576" s="64" t="n">
         <f aca="false">J1576*K1576</f>
@@ -33988,6 +34090,7 @@
     <row r="1577" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1577" s="62"/>
       <c r="E1577" s="63"/>
+      <c r="G1577" s="63"/>
       <c r="H1577" s="63"/>
       <c r="I1577" s="64" t="n">
         <f aca="false">J1577*K1577</f>
@@ -34001,6 +34104,7 @@
     <row r="1578" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1578" s="62"/>
       <c r="E1578" s="63"/>
+      <c r="G1578" s="63"/>
       <c r="H1578" s="63"/>
       <c r="I1578" s="64" t="n">
         <f aca="false">J1578*K1578</f>
@@ -34014,6 +34118,7 @@
     <row r="1579" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1579" s="62"/>
       <c r="E1579" s="63"/>
+      <c r="G1579" s="63"/>
       <c r="H1579" s="63"/>
       <c r="I1579" s="64" t="n">
         <f aca="false">J1579*K1579</f>
@@ -34027,6 +34132,7 @@
     <row r="1580" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1580" s="62"/>
       <c r="E1580" s="63"/>
+      <c r="G1580" s="63"/>
       <c r="H1580" s="63"/>
       <c r="I1580" s="64" t="n">
         <f aca="false">J1580*K1580</f>
@@ -34040,6 +34146,7 @@
     <row r="1581" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1581" s="62"/>
       <c r="E1581" s="63"/>
+      <c r="G1581" s="63"/>
       <c r="H1581" s="63"/>
       <c r="I1581" s="64" t="n">
         <f aca="false">J1581*K1581</f>
@@ -34053,6 +34160,7 @@
     <row r="1582" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1582" s="62"/>
       <c r="E1582" s="63"/>
+      <c r="G1582" s="63"/>
       <c r="H1582" s="63"/>
       <c r="I1582" s="64" t="n">
         <f aca="false">J1582*K1582</f>
@@ -34066,6 +34174,7 @@
     <row r="1583" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1583" s="62"/>
       <c r="E1583" s="63"/>
+      <c r="G1583" s="63"/>
       <c r="H1583" s="63"/>
       <c r="I1583" s="64" t="n">
         <f aca="false">J1583*K1583</f>
@@ -34079,6 +34188,7 @@
     <row r="1584" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1584" s="62"/>
       <c r="E1584" s="63"/>
+      <c r="G1584" s="63"/>
       <c r="H1584" s="63"/>
       <c r="I1584" s="64" t="n">
         <f aca="false">J1584*K1584</f>
@@ -34092,6 +34202,7 @@
     <row r="1585" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1585" s="62"/>
       <c r="E1585" s="63"/>
+      <c r="G1585" s="63"/>
       <c r="H1585" s="63"/>
       <c r="I1585" s="64" t="n">
         <f aca="false">J1585*K1585</f>
@@ -34105,6 +34216,7 @@
     <row r="1586" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1586" s="62"/>
       <c r="E1586" s="63"/>
+      <c r="G1586" s="63"/>
       <c r="H1586" s="63"/>
       <c r="I1586" s="64" t="n">
         <f aca="false">J1586*K1586</f>
@@ -34118,6 +34230,7 @@
     <row r="1587" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1587" s="62"/>
       <c r="E1587" s="63"/>
+      <c r="G1587" s="63"/>
       <c r="H1587" s="63"/>
       <c r="I1587" s="64" t="n">
         <f aca="false">J1587*K1587</f>
@@ -34131,6 +34244,7 @@
     <row r="1588" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1588" s="62"/>
       <c r="E1588" s="63"/>
+      <c r="G1588" s="63"/>
       <c r="H1588" s="63"/>
       <c r="I1588" s="64" t="n">
         <f aca="false">J1588*K1588</f>
@@ -34144,6 +34258,7 @@
     <row r="1589" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1589" s="62"/>
       <c r="E1589" s="63"/>
+      <c r="G1589" s="63"/>
       <c r="H1589" s="63"/>
       <c r="I1589" s="64" t="n">
         <f aca="false">J1589*K1589</f>
@@ -34157,6 +34272,7 @@
     <row r="1590" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1590" s="62"/>
       <c r="E1590" s="63"/>
+      <c r="G1590" s="63"/>
       <c r="H1590" s="63"/>
       <c r="I1590" s="64" t="n">
         <f aca="false">J1590*K1590</f>
@@ -34170,6 +34286,7 @@
     <row r="1591" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1591" s="62"/>
       <c r="E1591" s="63"/>
+      <c r="G1591" s="63"/>
       <c r="H1591" s="63"/>
       <c r="I1591" s="64" t="n">
         <f aca="false">J1591*K1591</f>
@@ -34183,6 +34300,7 @@
     <row r="1592" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1592" s="62"/>
       <c r="E1592" s="63"/>
+      <c r="G1592" s="63"/>
       <c r="H1592" s="63"/>
       <c r="I1592" s="64" t="n">
         <f aca="false">J1592*K1592</f>
@@ -34196,6 +34314,7 @@
     <row r="1593" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1593" s="62"/>
       <c r="E1593" s="63"/>
+      <c r="G1593" s="63"/>
       <c r="H1593" s="63"/>
       <c r="I1593" s="64" t="n">
         <f aca="false">J1593*K1593</f>
@@ -34209,6 +34328,7 @@
     <row r="1594" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1594" s="62"/>
       <c r="E1594" s="63"/>
+      <c r="G1594" s="63"/>
       <c r="H1594" s="63"/>
       <c r="I1594" s="64" t="n">
         <f aca="false">J1594*K1594</f>
@@ -34222,6 +34342,7 @@
     <row r="1595" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1595" s="62"/>
       <c r="E1595" s="63"/>
+      <c r="G1595" s="63"/>
       <c r="H1595" s="63"/>
       <c r="I1595" s="64" t="n">
         <f aca="false">J1595*K1595</f>
@@ -34235,6 +34356,7 @@
     <row r="1596" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1596" s="62"/>
       <c r="E1596" s="63"/>
+      <c r="G1596" s="63"/>
       <c r="H1596" s="63"/>
       <c r="I1596" s="64" t="n">
         <f aca="false">J1596*K1596</f>
@@ -34248,6 +34370,7 @@
     <row r="1597" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1597" s="62"/>
       <c r="E1597" s="63"/>
+      <c r="G1597" s="63"/>
       <c r="H1597" s="63"/>
       <c r="I1597" s="64" t="n">
         <f aca="false">J1597*K1597</f>
@@ -34261,6 +34384,7 @@
     <row r="1598" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1598" s="62"/>
       <c r="E1598" s="63"/>
+      <c r="G1598" s="63"/>
       <c r="H1598" s="63"/>
       <c r="I1598" s="64" t="n">
         <f aca="false">J1598*K1598</f>
@@ -34274,6 +34398,7 @@
     <row r="1599" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1599" s="62"/>
       <c r="E1599" s="63"/>
+      <c r="G1599" s="63"/>
       <c r="H1599" s="63"/>
       <c r="I1599" s="64" t="n">
         <f aca="false">J1599*K1599</f>
@@ -34287,6 +34412,7 @@
     <row r="1600" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1600" s="62"/>
       <c r="E1600" s="63"/>
+      <c r="G1600" s="63"/>
       <c r="H1600" s="63"/>
       <c r="I1600" s="64" t="n">
         <f aca="false">J1600*K1600</f>
@@ -34300,6 +34426,7 @@
     <row r="1601" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1601" s="62"/>
       <c r="E1601" s="63"/>
+      <c r="G1601" s="63"/>
       <c r="H1601" s="63"/>
       <c r="I1601" s="64" t="n">
         <f aca="false">J1601*K1601</f>
@@ -34312,6 +34439,7 @@
     <row r="1602" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1602" s="62"/>
       <c r="E1602" s="63"/>
+      <c r="G1602" s="63"/>
       <c r="H1602" s="63"/>
       <c r="I1602" s="64" t="n">
         <f aca="false">J1602*K1602</f>
@@ -34324,6 +34452,7 @@
     <row r="1603" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1603" s="62"/>
       <c r="E1603" s="63"/>
+      <c r="G1603" s="63"/>
       <c r="H1603" s="63"/>
       <c r="I1603" s="64" t="n">
         <f aca="false">J1603*K1603</f>
@@ -34336,6 +34465,7 @@
     <row r="1604" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1604" s="62"/>
       <c r="E1604" s="63"/>
+      <c r="G1604" s="63"/>
       <c r="H1604" s="63"/>
       <c r="I1604" s="64" t="n">
         <f aca="false">J1604*K1604</f>
@@ -34348,6 +34478,7 @@
     <row r="1605" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1605" s="62"/>
       <c r="E1605" s="63"/>
+      <c r="G1605" s="63"/>
       <c r="H1605" s="63"/>
       <c r="I1605" s="64" t="n">
         <f aca="false">J1605*K1605</f>
@@ -34360,6 +34491,7 @@
     <row r="1606" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1606" s="62"/>
       <c r="E1606" s="63"/>
+      <c r="G1606" s="63"/>
       <c r="H1606" s="63"/>
       <c r="I1606" s="64" t="n">
         <f aca="false">J1606*K1606</f>
@@ -34372,6 +34504,7 @@
     <row r="1607" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1607" s="62"/>
       <c r="E1607" s="63"/>
+      <c r="G1607" s="63"/>
       <c r="H1607" s="63"/>
       <c r="I1607" s="64" t="n">
         <f aca="false">J1607*K1607</f>
@@ -34384,6 +34517,7 @@
     <row r="1608" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1608" s="62"/>
       <c r="E1608" s="63"/>
+      <c r="G1608" s="63"/>
       <c r="H1608" s="63"/>
       <c r="I1608" s="64" t="n">
         <f aca="false">J1608*K1608</f>
@@ -34396,6 +34530,7 @@
     <row r="1609" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D1609" s="62"/>
       <c r="E1609" s="63"/>
+      <c r="G1609" s="63"/>
       <c r="H1609" s="63"/>
       <c r="I1609" s="64" t="n">
         <f aca="false">J1609*K1609</f>
@@ -34407,6 +34542,7 @@
     </row>
     <row r="1610" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1610" s="63"/>
+      <c r="G1610" s="63"/>
       <c r="H1610" s="63"/>
       <c r="I1610" s="64" t="n">
         <f aca="false">J1610*K1610</f>
@@ -34418,6 +34554,7 @@
     </row>
     <row r="1611" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1611" s="63"/>
+      <c r="G1611" s="63"/>
       <c r="H1611" s="63"/>
       <c r="I1611" s="64" t="n">
         <f aca="false">J1611*K1611</f>
@@ -34429,6 +34566,7 @@
     </row>
     <row r="1612" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1612" s="63"/>
+      <c r="G1612" s="63"/>
       <c r="H1612" s="63"/>
       <c r="I1612" s="64" t="n">
         <f aca="false">J1612*K1612</f>
@@ -34440,6 +34578,7 @@
     </row>
     <row r="1613" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1613" s="63"/>
+      <c r="G1613" s="63"/>
       <c r="H1613" s="63"/>
       <c r="I1613" s="64" t="n">
         <f aca="false">J1613*K1613</f>
@@ -34451,6 +34590,7 @@
     </row>
     <row r="1614" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1614" s="63"/>
+      <c r="G1614" s="63"/>
       <c r="H1614" s="63"/>
       <c r="I1614" s="64" t="n">
         <f aca="false">J1614*K1614</f>
@@ -34462,6 +34602,7 @@
     </row>
     <row r="1615" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1615" s="63"/>
+      <c r="G1615" s="63"/>
       <c r="H1615" s="63"/>
       <c r="I1615" s="64" t="n">
         <f aca="false">J1615*K1615</f>
@@ -34473,6 +34614,7 @@
     </row>
     <row r="1616" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1616" s="63"/>
+      <c r="G1616" s="63"/>
       <c r="H1616" s="63"/>
       <c r="I1616" s="64" t="n">
         <f aca="false">J1616*K1616</f>
@@ -34484,6 +34626,7 @@
     </row>
     <row r="1617" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1617" s="63"/>
+      <c r="G1617" s="63"/>
       <c r="H1617" s="63"/>
       <c r="I1617" s="64" t="n">
         <f aca="false">J1617*K1617</f>
@@ -34495,6 +34638,7 @@
     </row>
     <row r="1618" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1618" s="63"/>
+      <c r="G1618" s="63"/>
       <c r="H1618" s="63"/>
       <c r="I1618" s="64" t="n">
         <f aca="false">J1618*K1618</f>
@@ -34506,6 +34650,7 @@
     </row>
     <row r="1619" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1619" s="63"/>
+      <c r="G1619" s="63"/>
       <c r="H1619" s="63"/>
       <c r="I1619" s="64" t="n">
         <f aca="false">J1619*K1619</f>
@@ -34517,6 +34662,7 @@
     </row>
     <row r="1620" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1620" s="63"/>
+      <c r="G1620" s="63"/>
       <c r="H1620" s="63"/>
       <c r="I1620" s="64" t="n">
         <f aca="false">J1620*K1620</f>
@@ -34528,6 +34674,7 @@
     </row>
     <row r="1621" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1621" s="63"/>
+      <c r="G1621" s="63"/>
       <c r="H1621" s="63"/>
       <c r="I1621" s="64" t="n">
         <f aca="false">J1621*K1621</f>
@@ -34539,6 +34686,7 @@
     </row>
     <row r="1622" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1622" s="63"/>
+      <c r="G1622" s="63"/>
       <c r="H1622" s="63"/>
       <c r="I1622" s="64" t="n">
         <f aca="false">J1622*K1622</f>
@@ -34550,6 +34698,7 @@
     </row>
     <row r="1623" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1623" s="63"/>
+      <c r="G1623" s="63"/>
       <c r="H1623" s="63"/>
       <c r="I1623" s="64" t="n">
         <f aca="false">J1623*K1623</f>
@@ -34561,6 +34710,7 @@
     </row>
     <row r="1624" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1624" s="63"/>
+      <c r="G1624" s="63"/>
       <c r="H1624" s="7"/>
       <c r="I1624" s="64" t="n">
         <f aca="false">J1624*K1624</f>
@@ -34572,6 +34722,7 @@
     </row>
     <row r="1625" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1625" s="63"/>
+      <c r="G1625" s="63"/>
       <c r="H1625" s="7"/>
       <c r="I1625" s="64" t="n">
         <f aca="false">J1625*K1625</f>
@@ -34583,6 +34734,7 @@
     </row>
     <row r="1626" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1626" s="63"/>
+      <c r="G1626" s="63"/>
       <c r="H1626" s="7"/>
       <c r="I1626" s="64" t="n">
         <f aca="false">J1626*K1626</f>
@@ -34594,6 +34746,7 @@
     </row>
     <row r="1627" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1627" s="63"/>
+      <c r="G1627" s="63"/>
       <c r="H1627" s="7"/>
       <c r="I1627" s="64" t="n">
         <f aca="false">J1627*K1627</f>
@@ -34605,6 +34758,7 @@
     </row>
     <row r="1628" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1628" s="63"/>
+      <c r="G1628" s="63"/>
       <c r="H1628" s="7"/>
       <c r="I1628" s="64" t="n">
         <f aca="false">J1628*K1628</f>
@@ -34616,6 +34770,7 @@
     </row>
     <row r="1629" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1629" s="63"/>
+      <c r="G1629" s="63"/>
       <c r="H1629" s="7"/>
       <c r="I1629" s="64" t="n">
         <f aca="false">J1629*K1629</f>
@@ -34627,6 +34782,7 @@
     </row>
     <row r="1630" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1630" s="63"/>
+      <c r="G1630" s="63"/>
       <c r="H1630" s="7"/>
       <c r="I1630" s="64" t="n">
         <f aca="false">J1630*K1630</f>
@@ -34638,6 +34794,7 @@
     </row>
     <row r="1631" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1631" s="63"/>
+      <c r="G1631" s="63"/>
       <c r="H1631" s="7"/>
       <c r="I1631" s="64" t="n">
         <f aca="false">J1631*K1631</f>
@@ -34649,6 +34806,7 @@
     </row>
     <row r="1632" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1632" s="63"/>
+      <c r="G1632" s="63"/>
       <c r="H1632" s="7"/>
       <c r="I1632" s="64" t="n">
         <f aca="false">J1632*K1632</f>
@@ -34660,6 +34818,7 @@
     </row>
     <row r="1633" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1633" s="63"/>
+      <c r="G1633" s="63"/>
       <c r="H1633" s="7"/>
       <c r="I1633" s="64" t="n">
         <f aca="false">J1633*K1633</f>
@@ -34671,6 +34830,7 @@
     </row>
     <row r="1634" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1634" s="63"/>
+      <c r="G1634" s="63"/>
       <c r="H1634" s="7"/>
       <c r="I1634" s="64" t="n">
         <f aca="false">J1634*K1634</f>
@@ -34682,6 +34842,7 @@
     </row>
     <row r="1635" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1635" s="63"/>
+      <c r="G1635" s="63"/>
       <c r="H1635" s="7"/>
       <c r="I1635" s="64" t="n">
         <f aca="false">J1635*K1635</f>
@@ -34693,6 +34854,7 @@
     </row>
     <row r="1636" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1636" s="63"/>
+      <c r="G1636" s="63"/>
       <c r="H1636" s="7"/>
       <c r="I1636" s="64" t="n">
         <f aca="false">J1636*K1636</f>
@@ -34704,6 +34866,7 @@
     </row>
     <row r="1637" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1637" s="63"/>
+      <c r="G1637" s="63"/>
       <c r="H1637" s="7"/>
       <c r="I1637" s="64" t="n">
         <f aca="false">J1637*K1637</f>
@@ -34715,6 +34878,7 @@
     </row>
     <row r="1638" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1638" s="63"/>
+      <c r="G1638" s="63"/>
       <c r="H1638" s="7"/>
       <c r="I1638" s="64" t="n">
         <f aca="false">J1638*K1638</f>
@@ -34726,6 +34890,7 @@
     </row>
     <row r="1639" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1639" s="63"/>
+      <c r="G1639" s="63"/>
       <c r="H1639" s="7"/>
       <c r="I1639" s="64" t="n">
         <f aca="false">J1639*K1639</f>
@@ -34737,6 +34902,7 @@
     </row>
     <row r="1640" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1640" s="63"/>
+      <c r="G1640" s="63"/>
       <c r="H1640" s="7"/>
       <c r="I1640" s="64" t="n">
         <f aca="false">J1640*K1640</f>
@@ -34748,6 +34914,7 @@
     </row>
     <row r="1641" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1641" s="63"/>
+      <c r="G1641" s="63"/>
       <c r="H1641" s="7"/>
       <c r="I1641" s="64" t="n">
         <f aca="false">J1641*K1641</f>
@@ -34759,6 +34926,7 @@
     </row>
     <row r="1642" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1642" s="63"/>
+      <c r="G1642" s="63"/>
       <c r="H1642" s="7"/>
       <c r="I1642" s="64" t="n">
         <f aca="false">J1642*K1642</f>
@@ -34770,6 +34938,7 @@
     </row>
     <row r="1643" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1643" s="63"/>
+      <c r="G1643" s="63"/>
       <c r="H1643" s="7"/>
       <c r="I1643" s="64" t="n">
         <f aca="false">J1643*K1643</f>
@@ -34781,6 +34950,7 @@
     </row>
     <row r="1644" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E1644" s="63"/>
+      <c r="G1644" s="63"/>
       <c r="H1644" s="7"/>
       <c r="I1644" s="64" t="n">
         <f aca="false">J1644*K1644</f>
@@ -34791,6 +34961,7 @@
       <c r="T1644" s="1"/>
     </row>
     <row r="1645" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1645" s="63"/>
       <c r="H1645" s="7"/>
       <c r="I1645" s="64" t="n">
         <f aca="false">J1645*K1645</f>
@@ -34801,6 +34972,7 @@
       <c r="T1645" s="1"/>
     </row>
     <row r="1646" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1646" s="63"/>
       <c r="H1646" s="7"/>
       <c r="I1646" s="64" t="n">
         <f aca="false">J1646*K1646</f>
@@ -34811,6 +34983,7 @@
       <c r="T1646" s="1"/>
     </row>
     <row r="1647" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1647" s="63"/>
       <c r="H1647" s="7"/>
       <c r="I1647" s="64" t="n">
         <f aca="false">J1647*K1647</f>
@@ -34821,6 +34994,7 @@
       <c r="T1647" s="1"/>
     </row>
     <row r="1648" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1648" s="63"/>
       <c r="H1648" s="7"/>
       <c r="I1648" s="64" t="n">
         <f aca="false">J1648*K1648</f>
@@ -34831,6 +35005,7 @@
       <c r="T1648" s="1"/>
     </row>
     <row r="1649" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1649" s="63"/>
       <c r="H1649" s="7"/>
       <c r="I1649" s="64" t="n">
         <f aca="false">J1649*K1649</f>
@@ -34841,6 +35016,7 @@
       <c r="T1649" s="1"/>
     </row>
     <row r="1650" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1650" s="63"/>
       <c r="H1650" s="7"/>
       <c r="I1650" s="64" t="n">
         <f aca="false">J1650*K1650</f>
@@ -34851,6 +35027,7 @@
       <c r="T1650" s="1"/>
     </row>
     <row r="1651" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1651" s="63"/>
       <c r="H1651" s="7"/>
       <c r="I1651" s="64" t="n">
         <f aca="false">J1651*K1651</f>
@@ -34861,6 +35038,7 @@
       <c r="T1651" s="1"/>
     </row>
     <row r="1652" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1652" s="63"/>
       <c r="H1652" s="7"/>
       <c r="I1652" s="64" t="n">
         <f aca="false">J1652*K1652</f>
@@ -34871,6 +35049,7 @@
       <c r="T1652" s="1"/>
     </row>
     <row r="1653" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1653" s="63"/>
       <c r="H1653" s="7"/>
       <c r="I1653" s="64" t="n">
         <f aca="false">J1653*K1653</f>
@@ -34881,6 +35060,7 @@
       <c r="T1653" s="1"/>
     </row>
     <row r="1654" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1654" s="63"/>
       <c r="H1654" s="7"/>
       <c r="I1654" s="64" t="n">
         <f aca="false">J1654*K1654</f>
@@ -34891,6 +35071,7 @@
       <c r="T1654" s="1"/>
     </row>
     <row r="1655" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1655" s="63"/>
       <c r="H1655" s="7"/>
       <c r="I1655" s="64" t="n">
         <f aca="false">J1655*K1655</f>
@@ -34901,6 +35082,7 @@
       <c r="T1655" s="1"/>
     </row>
     <row r="1656" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1656" s="63"/>
       <c r="H1656" s="7"/>
       <c r="I1656" s="64" t="n">
         <f aca="false">J1656*K1656</f>
@@ -34911,6 +35093,7 @@
       <c r="T1656" s="1"/>
     </row>
     <row r="1657" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1657" s="63"/>
       <c r="H1657" s="7"/>
       <c r="I1657" s="64" t="n">
         <f aca="false">J1657*K1657</f>
@@ -34921,6 +35104,7 @@
       <c r="T1657" s="1"/>
     </row>
     <row r="1658" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1658" s="63"/>
       <c r="H1658" s="7"/>
       <c r="I1658" s="64" t="n">
         <f aca="false">J1658*K1658</f>
@@ -34931,6 +35115,7 @@
       <c r="T1658" s="1"/>
     </row>
     <row r="1659" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1659" s="63"/>
       <c r="H1659" s="7"/>
       <c r="I1659" s="64" t="n">
         <f aca="false">J1659*K1659</f>
@@ -34941,6 +35126,7 @@
       <c r="T1659" s="1"/>
     </row>
     <row r="1660" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1660" s="63"/>
       <c r="H1660" s="7"/>
       <c r="I1660" s="64" t="n">
         <f aca="false">J1660*K1660</f>
@@ -34951,6 +35137,7 @@
       <c r="T1660" s="1"/>
     </row>
     <row r="1661" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1661" s="63"/>
       <c r="H1661" s="7"/>
       <c r="I1661" s="64" t="n">
         <f aca="false">J1661*K1661</f>
@@ -34961,6 +35148,7 @@
       <c r="T1661" s="1"/>
     </row>
     <row r="1662" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1662" s="63"/>
       <c r="H1662" s="7"/>
       <c r="I1662" s="64" t="n">
         <f aca="false">J1662*K1662</f>
@@ -34971,6 +35159,7 @@
       <c r="T1662" s="1"/>
     </row>
     <row r="1663" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1663" s="63"/>
       <c r="H1663" s="7"/>
       <c r="I1663" s="64" t="n">
         <f aca="false">J1663*K1663</f>
@@ -34981,6 +35170,7 @@
       <c r="T1663" s="1"/>
     </row>
     <row r="1664" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1664" s="63"/>
       <c r="H1664" s="7"/>
       <c r="I1664" s="64" t="n">
         <f aca="false">J1664*K1664</f>
@@ -34991,6 +35181,7 @@
       <c r="T1664" s="1"/>
     </row>
     <row r="1665" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1665" s="63"/>
       <c r="H1665" s="7"/>
       <c r="I1665" s="64" t="n">
         <f aca="false">J1665*K1665</f>
@@ -35001,6 +35192,7 @@
       <c r="T1665" s="1"/>
     </row>
     <row r="1666" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1666" s="63"/>
       <c r="H1666" s="7"/>
       <c r="I1666" s="64" t="n">
         <f aca="false">J1666*K1666</f>
@@ -35011,6 +35203,7 @@
       <c r="T1666" s="1"/>
     </row>
     <row r="1667" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1667" s="63"/>
       <c r="H1667" s="7"/>
       <c r="I1667" s="64" t="n">
         <f aca="false">J1667*K1667</f>
@@ -35021,6 +35214,7 @@
       <c r="T1667" s="1"/>
     </row>
     <row r="1668" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1668" s="63"/>
       <c r="H1668" s="7"/>
       <c r="I1668" s="64" t="n">
         <f aca="false">J1668*K1668</f>
@@ -35031,6 +35225,7 @@
       <c r="T1668" s="1"/>
     </row>
     <row r="1669" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1669" s="63"/>
       <c r="H1669" s="7"/>
       <c r="I1669" s="64" t="n">
         <f aca="false">J1669*K1669</f>
@@ -35041,6 +35236,7 @@
       <c r="T1669" s="1"/>
     </row>
     <row r="1670" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1670" s="63"/>
       <c r="H1670" s="7"/>
       <c r="I1670" s="64" t="n">
         <f aca="false">J1670*K1670</f>
@@ -35051,6 +35247,7 @@
       <c r="T1670" s="1"/>
     </row>
     <row r="1671" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1671" s="63"/>
       <c r="H1671" s="7"/>
       <c r="I1671" s="64" t="n">
         <f aca="false">J1671*K1671</f>
@@ -35061,6 +35258,7 @@
       <c r="T1671" s="1"/>
     </row>
     <row r="1672" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1672" s="63"/>
       <c r="H1672" s="7"/>
       <c r="I1672" s="64" t="n">
         <f aca="false">J1672*K1672</f>
@@ -35071,6 +35269,7 @@
       <c r="T1672" s="1"/>
     </row>
     <row r="1673" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1673" s="63"/>
       <c r="H1673" s="7"/>
       <c r="I1673" s="64" t="n">
         <f aca="false">J1673*K1673</f>
@@ -35081,6 +35280,7 @@
       <c r="T1673" s="1"/>
     </row>
     <row r="1674" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1674" s="63"/>
       <c r="H1674" s="7"/>
       <c r="I1674" s="64" t="n">
         <f aca="false">J1674*K1674</f>
@@ -35091,6 +35291,7 @@
       <c r="T1674" s="1"/>
     </row>
     <row r="1675" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1675" s="63"/>
       <c r="H1675" s="7"/>
       <c r="I1675" s="64" t="n">
         <f aca="false">J1675*K1675</f>
@@ -35101,6 +35302,7 @@
       <c r="T1675" s="1"/>
     </row>
     <row r="1676" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1676" s="63"/>
       <c r="H1676" s="7"/>
       <c r="I1676" s="64" t="n">
         <f aca="false">J1676*K1676</f>
@@ -35111,6 +35313,7 @@
       <c r="T1676" s="1"/>
     </row>
     <row r="1677" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1677" s="63"/>
       <c r="H1677" s="7"/>
       <c r="I1677" s="64" t="n">
         <f aca="false">J1677*K1677</f>
@@ -35121,6 +35324,7 @@
       <c r="T1677" s="1"/>
     </row>
     <row r="1678" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1678" s="63"/>
       <c r="H1678" s="7"/>
       <c r="I1678" s="64" t="n">
         <f aca="false">J1678*K1678</f>
@@ -35131,6 +35335,7 @@
       <c r="T1678" s="1"/>
     </row>
     <row r="1679" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1679" s="63"/>
       <c r="H1679" s="7"/>
       <c r="I1679" s="64" t="n">
         <f aca="false">J1679*K1679</f>
@@ -35141,6 +35346,7 @@
       <c r="T1679" s="1"/>
     </row>
     <row r="1680" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1680" s="63"/>
       <c r="H1680" s="7"/>
       <c r="I1680" s="64" t="n">
         <f aca="false">J1680*K1680</f>
@@ -35151,6 +35357,7 @@
       <c r="T1680" s="1"/>
     </row>
     <row r="1681" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1681" s="63"/>
       <c r="H1681" s="7"/>
       <c r="I1681" s="64" t="n">
         <f aca="false">J1681*K1681</f>
@@ -35161,6 +35368,7 @@
       <c r="T1681" s="1"/>
     </row>
     <row r="1682" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1682" s="63"/>
       <c r="H1682" s="7"/>
       <c r="I1682" s="64" t="n">
         <f aca="false">J1682*K1682</f>
@@ -35171,6 +35379,7 @@
       <c r="T1682" s="1"/>
     </row>
     <row r="1683" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1683" s="63"/>
       <c r="H1683" s="7"/>
       <c r="I1683" s="64" t="n">
         <f aca="false">J1683*K1683</f>
@@ -35181,6 +35390,7 @@
       <c r="T1683" s="1"/>
     </row>
     <row r="1684" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1684" s="63"/>
       <c r="H1684" s="7"/>
       <c r="I1684" s="64" t="n">
         <f aca="false">J1684*K1684</f>
@@ -35191,6 +35401,7 @@
       <c r="T1684" s="1"/>
     </row>
     <row r="1685" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1685" s="63"/>
       <c r="H1685" s="7"/>
       <c r="I1685" s="64" t="n">
         <f aca="false">J1685*K1685</f>
@@ -35201,6 +35412,7 @@
       <c r="T1685" s="1"/>
     </row>
     <row r="1686" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1686" s="63"/>
       <c r="H1686" s="7"/>
       <c r="I1686" s="64" t="n">
         <f aca="false">J1686*K1686</f>
@@ -35211,981 +35423,1291 @@
       <c r="T1686" s="1"/>
     </row>
     <row r="1687" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1687" s="63"/>
       <c r="H1687" s="7"/>
       <c r="R1687" s="63"/>
       <c r="S1687" s="1"/>
       <c r="T1687" s="1"/>
     </row>
     <row r="1688" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1688" s="63"/>
       <c r="H1688" s="7"/>
       <c r="R1688" s="63"/>
       <c r="S1688" s="1"/>
       <c r="T1688" s="1"/>
     </row>
     <row r="1689" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1689" s="63"/>
       <c r="H1689" s="7"/>
       <c r="R1689" s="63"/>
       <c r="S1689" s="1"/>
       <c r="T1689" s="1"/>
     </row>
     <row r="1690" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1690" s="63"/>
       <c r="H1690" s="7"/>
       <c r="R1690" s="63"/>
       <c r="S1690" s="1"/>
       <c r="T1690" s="1"/>
     </row>
     <row r="1691" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1691" s="63"/>
       <c r="H1691" s="7"/>
       <c r="R1691" s="63"/>
       <c r="S1691" s="1"/>
       <c r="T1691" s="1"/>
     </row>
     <row r="1692" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1692" s="63"/>
       <c r="H1692" s="7"/>
       <c r="R1692" s="63"/>
       <c r="S1692" s="1"/>
       <c r="T1692" s="1"/>
     </row>
     <row r="1693" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1693" s="63"/>
       <c r="H1693" s="7"/>
       <c r="R1693" s="63"/>
       <c r="S1693" s="1"/>
       <c r="T1693" s="1"/>
     </row>
     <row r="1694" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1694" s="63"/>
       <c r="H1694" s="7"/>
       <c r="R1694" s="63"/>
       <c r="S1694" s="1"/>
       <c r="T1694" s="1"/>
     </row>
     <row r="1695" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1695" s="63"/>
       <c r="H1695" s="7"/>
       <c r="R1695" s="63"/>
       <c r="S1695" s="1"/>
       <c r="T1695" s="1"/>
     </row>
     <row r="1696" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1696" s="63"/>
       <c r="H1696" s="7"/>
       <c r="R1696" s="63"/>
       <c r="S1696" s="1"/>
       <c r="T1696" s="1"/>
     </row>
     <row r="1697" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1697" s="63"/>
       <c r="H1697" s="7"/>
       <c r="R1697" s="63"/>
       <c r="S1697" s="1"/>
       <c r="T1697" s="1"/>
     </row>
     <row r="1698" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1698" s="63"/>
       <c r="H1698" s="7"/>
       <c r="R1698" s="63"/>
       <c r="S1698" s="1"/>
       <c r="T1698" s="1"/>
     </row>
     <row r="1699" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1699" s="63"/>
       <c r="H1699" s="7"/>
       <c r="R1699" s="63"/>
       <c r="S1699" s="1"/>
       <c r="T1699" s="1"/>
     </row>
     <row r="1700" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1700" s="63"/>
       <c r="H1700" s="7"/>
       <c r="R1700" s="63"/>
       <c r="S1700" s="1"/>
       <c r="T1700" s="1"/>
     </row>
     <row r="1701" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1701" s="63"/>
       <c r="H1701" s="7"/>
       <c r="R1701" s="63"/>
       <c r="S1701" s="1"/>
       <c r="T1701" s="1"/>
     </row>
     <row r="1702" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1702" s="63"/>
       <c r="H1702" s="7"/>
       <c r="R1702" s="63"/>
       <c r="S1702" s="1"/>
       <c r="T1702" s="1"/>
     </row>
     <row r="1703" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1703" s="63"/>
       <c r="H1703" s="7"/>
     </row>
     <row r="1704" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1704" s="63"/>
       <c r="H1704" s="7"/>
     </row>
     <row r="1705" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1705" s="63"/>
       <c r="H1705" s="7"/>
     </row>
     <row r="1706" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1706" s="63"/>
       <c r="H1706" s="7"/>
     </row>
     <row r="1707" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1707" s="63"/>
       <c r="H1707" s="7"/>
     </row>
     <row r="1708" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1708" s="63"/>
       <c r="H1708" s="7"/>
     </row>
     <row r="1709" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1709" s="63"/>
       <c r="H1709" s="7"/>
     </row>
     <row r="1710" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1710" s="63"/>
       <c r="H1710" s="7"/>
     </row>
     <row r="1711" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1711" s="63"/>
       <c r="H1711" s="7"/>
     </row>
     <row r="1712" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1712" s="63"/>
       <c r="H1712" s="7"/>
     </row>
     <row r="1713" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1713" s="63"/>
       <c r="H1713" s="7"/>
     </row>
     <row r="1714" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1714" s="63"/>
       <c r="H1714" s="7"/>
     </row>
     <row r="1715" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1715" s="63"/>
       <c r="H1715" s="7"/>
     </row>
     <row r="1716" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1716" s="63"/>
       <c r="H1716" s="7"/>
     </row>
     <row r="1717" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1717" s="63"/>
       <c r="H1717" s="7"/>
     </row>
     <row r="1718" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1718" s="63"/>
       <c r="H1718" s="7"/>
     </row>
     <row r="1719" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1719" s="63"/>
       <c r="H1719" s="7"/>
     </row>
     <row r="1720" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1720" s="63"/>
       <c r="H1720" s="7"/>
     </row>
     <row r="1721" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1721" s="63"/>
       <c r="H1721" s="7"/>
     </row>
     <row r="1722" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1722" s="63"/>
       <c r="H1722" s="7"/>
     </row>
     <row r="1723" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1723" s="63"/>
       <c r="H1723" s="7"/>
     </row>
     <row r="1724" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1724" s="63"/>
       <c r="H1724" s="7"/>
     </row>
     <row r="1725" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1725" s="63"/>
       <c r="H1725" s="7"/>
     </row>
     <row r="1726" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1726" s="63"/>
       <c r="H1726" s="7"/>
     </row>
     <row r="1727" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1727" s="63"/>
       <c r="H1727" s="7"/>
     </row>
     <row r="1728" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1728" s="63"/>
       <c r="H1728" s="7"/>
     </row>
     <row r="1729" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1729" s="63"/>
       <c r="H1729" s="7"/>
     </row>
     <row r="1730" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1730" s="63"/>
       <c r="H1730" s="7"/>
     </row>
     <row r="1731" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1731" s="63"/>
       <c r="H1731" s="7"/>
     </row>
     <row r="1732" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1732" s="63"/>
       <c r="H1732" s="7"/>
     </row>
     <row r="1733" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1733" s="63"/>
       <c r="H1733" s="7"/>
     </row>
     <row r="1734" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1734" s="63"/>
       <c r="H1734" s="7"/>
     </row>
     <row r="1735" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1735" s="63"/>
       <c r="H1735" s="7"/>
     </row>
     <row r="1736" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1736" s="63"/>
       <c r="H1736" s="7"/>
     </row>
     <row r="1737" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1737" s="63"/>
       <c r="H1737" s="7"/>
     </row>
     <row r="1738" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1738" s="63"/>
       <c r="H1738" s="7"/>
     </row>
     <row r="1739" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1739" s="63"/>
       <c r="H1739" s="7"/>
     </row>
     <row r="1740" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1740" s="63"/>
       <c r="H1740" s="7"/>
     </row>
     <row r="1741" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1741" s="63"/>
       <c r="H1741" s="7"/>
     </row>
     <row r="1742" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1742" s="63"/>
       <c r="H1742" s="7"/>
     </row>
     <row r="1743" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1743" s="63"/>
       <c r="H1743" s="7"/>
     </row>
     <row r="1744" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1744" s="63"/>
       <c r="H1744" s="7"/>
     </row>
     <row r="1745" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1745" s="63"/>
       <c r="H1745" s="7"/>
     </row>
     <row r="1746" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1746" s="63"/>
       <c r="H1746" s="7"/>
     </row>
     <row r="1747" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1747" s="63"/>
       <c r="H1747" s="7"/>
     </row>
     <row r="1748" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1748" s="63"/>
       <c r="H1748" s="7"/>
     </row>
     <row r="1749" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1749" s="63"/>
       <c r="H1749" s="7"/>
     </row>
     <row r="1750" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1750" s="63"/>
       <c r="H1750" s="7"/>
     </row>
     <row r="1751" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1751" s="63"/>
       <c r="H1751" s="7"/>
     </row>
     <row r="1752" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1752" s="63"/>
       <c r="H1752" s="7"/>
     </row>
     <row r="1753" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1753" s="63"/>
       <c r="H1753" s="7"/>
     </row>
     <row r="1754" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1754" s="63"/>
       <c r="H1754" s="7"/>
     </row>
     <row r="1755" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1755" s="63"/>
       <c r="H1755" s="7"/>
     </row>
     <row r="1756" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1756" s="63"/>
       <c r="H1756" s="7"/>
     </row>
     <row r="1757" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1757" s="63"/>
       <c r="H1757" s="7"/>
     </row>
     <row r="1758" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1758" s="63"/>
       <c r="H1758" s="7"/>
     </row>
     <row r="1759" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1759" s="63"/>
       <c r="H1759" s="7"/>
     </row>
     <row r="1760" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1760" s="63"/>
       <c r="H1760" s="7"/>
     </row>
     <row r="1761" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1761" s="63"/>
       <c r="H1761" s="7"/>
     </row>
     <row r="1762" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1762" s="63"/>
       <c r="H1762" s="7"/>
     </row>
     <row r="1763" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1763" s="63"/>
       <c r="H1763" s="7"/>
     </row>
     <row r="1764" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1764" s="63"/>
       <c r="H1764" s="7"/>
     </row>
     <row r="1765" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1765" s="63"/>
       <c r="H1765" s="7"/>
     </row>
     <row r="1766" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1766" s="63"/>
       <c r="H1766" s="7"/>
     </row>
     <row r="1767" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1767" s="63"/>
       <c r="H1767" s="7"/>
     </row>
     <row r="1768" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1768" s="63"/>
       <c r="H1768" s="7"/>
     </row>
     <row r="1769" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1769" s="63"/>
       <c r="H1769" s="7"/>
     </row>
     <row r="1770" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1770" s="63"/>
       <c r="H1770" s="7"/>
     </row>
     <row r="1771" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1771" s="63"/>
       <c r="H1771" s="7"/>
     </row>
     <row r="1772" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1772" s="63"/>
       <c r="H1772" s="7"/>
     </row>
     <row r="1773" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1773" s="63"/>
       <c r="H1773" s="7"/>
     </row>
     <row r="1774" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1774" s="63"/>
       <c r="H1774" s="7"/>
     </row>
     <row r="1775" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1775" s="63"/>
       <c r="H1775" s="7"/>
     </row>
     <row r="1776" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1776" s="63"/>
       <c r="H1776" s="7"/>
     </row>
     <row r="1777" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1777" s="63"/>
       <c r="H1777" s="7"/>
     </row>
     <row r="1778" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1778" s="63"/>
       <c r="H1778" s="7"/>
     </row>
     <row r="1779" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1779" s="63"/>
       <c r="H1779" s="7"/>
     </row>
     <row r="1780" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1780" s="63"/>
       <c r="H1780" s="7"/>
     </row>
     <row r="1781" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1781" s="63"/>
       <c r="H1781" s="7"/>
     </row>
     <row r="1782" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1782" s="63"/>
       <c r="H1782" s="7"/>
     </row>
     <row r="1783" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1783" s="63"/>
       <c r="H1783" s="7"/>
     </row>
     <row r="1784" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1784" s="63"/>
       <c r="H1784" s="7"/>
     </row>
     <row r="1785" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1785" s="63"/>
       <c r="H1785" s="7"/>
     </row>
     <row r="1786" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1786" s="63"/>
       <c r="H1786" s="7"/>
     </row>
     <row r="1787" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1787" s="63"/>
       <c r="H1787" s="7"/>
     </row>
     <row r="1788" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1788" s="63"/>
       <c r="H1788" s="7"/>
     </row>
     <row r="1789" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1789" s="63"/>
       <c r="H1789" s="7"/>
     </row>
     <row r="1790" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1790" s="63"/>
       <c r="H1790" s="7"/>
     </row>
     <row r="1791" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1791" s="63"/>
       <c r="H1791" s="7"/>
     </row>
     <row r="1792" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1792" s="63"/>
       <c r="H1792" s="7"/>
     </row>
     <row r="1793" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1793" s="63"/>
       <c r="H1793" s="7"/>
     </row>
     <row r="1794" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1794" s="63"/>
       <c r="H1794" s="7"/>
     </row>
     <row r="1795" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1795" s="63"/>
       <c r="H1795" s="7"/>
     </row>
     <row r="1796" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1796" s="63"/>
       <c r="H1796" s="7"/>
     </row>
     <row r="1797" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1797" s="63"/>
       <c r="H1797" s="7"/>
     </row>
     <row r="1798" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1798" s="63"/>
       <c r="H1798" s="7"/>
     </row>
     <row r="1799" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1799" s="63"/>
       <c r="H1799" s="7"/>
     </row>
     <row r="1800" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1800" s="63"/>
       <c r="H1800" s="7"/>
     </row>
     <row r="1801" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1801" s="63"/>
       <c r="H1801" s="7"/>
     </row>
     <row r="1802" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1802" s="63"/>
       <c r="H1802" s="7"/>
     </row>
     <row r="1803" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1803" s="63"/>
       <c r="H1803" s="7"/>
     </row>
     <row r="1804" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1804" s="63"/>
       <c r="H1804" s="7"/>
     </row>
     <row r="1805" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1805" s="63"/>
       <c r="H1805" s="7"/>
     </row>
     <row r="1806" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1806" s="63"/>
       <c r="H1806" s="7"/>
     </row>
     <row r="1807" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1807" s="63"/>
       <c r="H1807" s="7"/>
     </row>
     <row r="1808" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1808" s="63"/>
       <c r="H1808" s="7"/>
     </row>
     <row r="1809" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1809" s="63"/>
       <c r="H1809" s="7"/>
     </row>
     <row r="1810" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1810" s="63"/>
       <c r="H1810" s="7"/>
     </row>
     <row r="1811" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1811" s="63"/>
       <c r="H1811" s="7"/>
     </row>
     <row r="1812" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1812" s="63"/>
       <c r="H1812" s="7"/>
     </row>
     <row r="1813" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1813" s="63"/>
       <c r="H1813" s="7"/>
     </row>
     <row r="1814" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1814" s="63"/>
       <c r="H1814" s="7"/>
     </row>
     <row r="1815" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1815" s="63"/>
       <c r="H1815" s="7"/>
     </row>
     <row r="1816" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1816" s="63"/>
       <c r="H1816" s="7"/>
     </row>
     <row r="1817" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1817" s="63"/>
       <c r="H1817" s="7"/>
     </row>
     <row r="1818" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1818" s="63"/>
       <c r="H1818" s="7"/>
     </row>
     <row r="1819" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1819" s="63"/>
       <c r="H1819" s="7"/>
     </row>
     <row r="1820" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1820" s="63"/>
       <c r="H1820" s="7"/>
     </row>
     <row r="1821" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1821" s="63"/>
       <c r="H1821" s="7"/>
     </row>
     <row r="1822" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1822" s="63"/>
       <c r="H1822" s="7"/>
     </row>
     <row r="1823" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1823" s="63"/>
       <c r="H1823" s="7"/>
     </row>
     <row r="1824" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1824" s="63"/>
       <c r="H1824" s="7"/>
     </row>
     <row r="1825" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1825" s="63"/>
       <c r="H1825" s="7"/>
     </row>
     <row r="1826" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1826" s="63"/>
       <c r="H1826" s="7"/>
     </row>
     <row r="1827" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1827" s="63"/>
       <c r="H1827" s="7"/>
     </row>
     <row r="1828" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1828" s="63"/>
       <c r="H1828" s="7"/>
     </row>
     <row r="1829" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1829" s="63"/>
       <c r="H1829" s="7"/>
     </row>
     <row r="1830" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1830" s="63"/>
       <c r="H1830" s="7"/>
     </row>
     <row r="1831" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1831" s="63"/>
       <c r="H1831" s="7"/>
     </row>
     <row r="1832" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1832" s="63"/>
       <c r="H1832" s="7"/>
     </row>
     <row r="1833" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1833" s="63"/>
       <c r="H1833" s="7"/>
     </row>
     <row r="1834" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1834" s="63"/>
       <c r="H1834" s="7"/>
     </row>
     <row r="1835" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1835" s="63"/>
       <c r="H1835" s="7"/>
     </row>
     <row r="1836" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1836" s="63"/>
       <c r="H1836" s="7"/>
     </row>
     <row r="1837" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1837" s="63"/>
       <c r="H1837" s="7"/>
     </row>
     <row r="1838" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1838" s="63"/>
       <c r="H1838" s="7"/>
     </row>
     <row r="1839" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1839" s="63"/>
       <c r="H1839" s="7"/>
     </row>
     <row r="1840" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1840" s="63"/>
       <c r="H1840" s="7"/>
     </row>
     <row r="1841" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1841" s="63"/>
       <c r="H1841" s="7"/>
     </row>
     <row r="1842" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1842" s="63"/>
       <c r="H1842" s="7"/>
     </row>
     <row r="1843" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1843" s="63"/>
       <c r="H1843" s="7"/>
     </row>
     <row r="1844" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1844" s="63"/>
       <c r="H1844" s="7"/>
     </row>
     <row r="1845" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1845" s="63"/>
       <c r="H1845" s="7"/>
     </row>
     <row r="1846" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1846" s="63"/>
       <c r="H1846" s="7"/>
     </row>
     <row r="1847" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1847" s="63"/>
       <c r="H1847" s="7"/>
     </row>
     <row r="1848" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1848" s="63"/>
       <c r="H1848" s="7"/>
     </row>
     <row r="1849" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1849" s="63"/>
       <c r="H1849" s="7"/>
     </row>
     <row r="1850" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1850" s="63"/>
       <c r="H1850" s="7"/>
     </row>
     <row r="1851" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1851" s="63"/>
       <c r="H1851" s="7"/>
     </row>
     <row r="1852" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1852" s="63"/>
       <c r="H1852" s="7"/>
     </row>
     <row r="1853" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1853" s="63"/>
       <c r="H1853" s="7"/>
     </row>
     <row r="1854" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1854" s="63"/>
       <c r="H1854" s="7"/>
     </row>
     <row r="1855" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1855" s="63"/>
       <c r="H1855" s="7"/>
     </row>
     <row r="1856" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1856" s="63"/>
       <c r="H1856" s="7"/>
     </row>
     <row r="1857" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1857" s="63"/>
       <c r="H1857" s="7"/>
     </row>
     <row r="1858" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1858" s="63"/>
       <c r="H1858" s="7"/>
     </row>
     <row r="1859" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1859" s="63"/>
       <c r="H1859" s="7"/>
     </row>
     <row r="1860" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1860" s="63"/>
       <c r="H1860" s="7"/>
     </row>
     <row r="1861" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1861" s="63"/>
       <c r="H1861" s="7"/>
     </row>
     <row r="1862" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1862" s="63"/>
       <c r="H1862" s="7"/>
     </row>
     <row r="1863" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1863" s="63"/>
       <c r="H1863" s="7"/>
     </row>
     <row r="1864" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1864" s="63"/>
       <c r="H1864" s="7"/>
     </row>
     <row r="1865" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1865" s="63"/>
       <c r="H1865" s="7"/>
     </row>
     <row r="1866" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1866" s="63"/>
       <c r="H1866" s="7"/>
     </row>
     <row r="1867" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1867" s="63"/>
       <c r="H1867" s="7"/>
     </row>
     <row r="1868" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1868" s="63"/>
       <c r="H1868" s="7"/>
     </row>
     <row r="1869" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1869" s="63"/>
       <c r="H1869" s="7"/>
     </row>
     <row r="1870" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1870" s="63"/>
       <c r="H1870" s="7"/>
     </row>
     <row r="1871" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1871" s="63"/>
       <c r="H1871" s="7"/>
     </row>
     <row r="1872" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1872" s="63"/>
       <c r="H1872" s="7"/>
     </row>
     <row r="1873" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1873" s="63"/>
       <c r="H1873" s="7"/>
     </row>
     <row r="1874" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1874" s="63"/>
       <c r="H1874" s="7"/>
     </row>
     <row r="1875" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1875" s="63"/>
       <c r="H1875" s="7"/>
     </row>
     <row r="1876" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1876" s="63"/>
       <c r="H1876" s="7"/>
     </row>
     <row r="1877" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1877" s="63"/>
       <c r="H1877" s="7"/>
     </row>
     <row r="1878" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1878" s="63"/>
       <c r="H1878" s="7"/>
     </row>
     <row r="1879" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1879" s="63"/>
       <c r="H1879" s="7"/>
     </row>
     <row r="1880" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1880" s="63"/>
       <c r="H1880" s="7"/>
     </row>
     <row r="1881" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1881" s="63"/>
       <c r="H1881" s="7"/>
     </row>
     <row r="1882" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1882" s="63"/>
       <c r="H1882" s="7"/>
     </row>
     <row r="1883" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1883" s="63"/>
       <c r="H1883" s="7"/>
     </row>
     <row r="1884" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1884" s="63"/>
       <c r="H1884" s="7"/>
     </row>
     <row r="1885" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1885" s="63"/>
       <c r="H1885" s="7"/>
     </row>
     <row r="1886" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1886" s="63"/>
       <c r="H1886" s="7"/>
     </row>
     <row r="1887" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1887" s="63"/>
       <c r="H1887" s="7"/>
     </row>
     <row r="1888" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1888" s="63"/>
       <c r="H1888" s="7"/>
     </row>
     <row r="1889" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1889" s="63"/>
       <c r="H1889" s="7"/>
     </row>
     <row r="1890" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1890" s="63"/>
       <c r="H1890" s="7"/>
     </row>
     <row r="1891" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1891" s="63"/>
       <c r="H1891" s="7"/>
     </row>
     <row r="1892" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1892" s="63"/>
       <c r="H1892" s="7"/>
     </row>
     <row r="1893" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1893" s="63"/>
       <c r="H1893" s="7"/>
     </row>
     <row r="1894" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1894" s="63"/>
       <c r="H1894" s="7"/>
     </row>
     <row r="1895" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1895" s="63"/>
       <c r="H1895" s="7"/>
     </row>
     <row r="1896" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1896" s="63"/>
       <c r="H1896" s="7"/>
     </row>
     <row r="1897" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1897" s="63"/>
       <c r="H1897" s="7"/>
     </row>
     <row r="1898" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1898" s="63"/>
       <c r="H1898" s="7"/>
     </row>
     <row r="1899" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1899" s="63"/>
       <c r="H1899" s="7"/>
     </row>
     <row r="1900" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1900" s="63"/>
       <c r="H1900" s="7"/>
     </row>
     <row r="1901" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1901" s="63"/>
       <c r="H1901" s="7"/>
     </row>
     <row r="1902" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1902" s="63"/>
       <c r="H1902" s="7"/>
     </row>
     <row r="1903" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1903" s="63"/>
       <c r="H1903" s="7"/>
     </row>
     <row r="1904" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1904" s="63"/>
       <c r="H1904" s="7"/>
     </row>
     <row r="1905" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1905" s="63"/>
       <c r="H1905" s="7"/>
     </row>
     <row r="1906" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1906" s="63"/>
       <c r="H1906" s="7"/>
     </row>
     <row r="1907" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1907" s="63"/>
       <c r="H1907" s="7"/>
     </row>
     <row r="1908" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1908" s="63"/>
       <c r="H1908" s="7"/>
     </row>
     <row r="1909" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1909" s="63"/>
       <c r="H1909" s="7"/>
     </row>
     <row r="1910" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1910" s="63"/>
       <c r="H1910" s="7"/>
     </row>
     <row r="1911" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1911" s="63"/>
       <c r="H1911" s="7"/>
     </row>
     <row r="1912" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1912" s="63"/>
       <c r="H1912" s="7"/>
     </row>
     <row r="1913" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1913" s="63"/>
       <c r="H1913" s="7"/>
     </row>
     <row r="1914" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1914" s="63"/>
       <c r="H1914" s="7"/>
     </row>
     <row r="1915" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1915" s="63"/>
       <c r="H1915" s="7"/>
     </row>
     <row r="1916" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1916" s="63"/>
       <c r="H1916" s="7"/>
     </row>
     <row r="1917" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1917" s="63"/>
       <c r="H1917" s="7"/>
     </row>
     <row r="1918" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1918" s="63"/>
       <c r="H1918" s="7"/>
     </row>
     <row r="1919" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1919" s="63"/>
       <c r="H1919" s="7"/>
     </row>
     <row r="1920" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1920" s="63"/>
       <c r="H1920" s="7"/>
     </row>
     <row r="1921" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1921" s="63"/>
       <c r="H1921" s="7"/>
     </row>
     <row r="1922" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1922" s="63"/>
       <c r="H1922" s="7"/>
     </row>
     <row r="1923" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1923" s="63"/>
       <c r="H1923" s="7"/>
     </row>
     <row r="1924" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1924" s="63"/>
       <c r="H1924" s="7"/>
     </row>
     <row r="1925" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1925" s="63"/>
       <c r="H1925" s="7"/>
     </row>
     <row r="1926" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1926" s="63"/>
       <c r="H1926" s="7"/>
     </row>
     <row r="1927" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1927" s="63"/>
       <c r="H1927" s="7"/>
     </row>
     <row r="1928" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1928" s="63"/>
       <c r="H1928" s="7"/>
     </row>
     <row r="1929" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1929" s="63"/>
       <c r="H1929" s="7"/>
     </row>
     <row r="1930" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1930" s="63"/>
       <c r="H1930" s="7"/>
     </row>
     <row r="1931" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1931" s="63"/>
       <c r="H1931" s="7"/>
     </row>
     <row r="1932" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1932" s="63"/>
       <c r="H1932" s="7"/>
     </row>
     <row r="1933" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1933" s="63"/>
       <c r="H1933" s="7"/>
     </row>
     <row r="1934" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1934" s="63"/>
       <c r="H1934" s="7"/>
     </row>
     <row r="1935" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1935" s="63"/>
       <c r="H1935" s="7"/>
     </row>
     <row r="1936" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1936" s="63"/>
       <c r="H1936" s="7"/>
     </row>
     <row r="1937" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1937" s="63"/>
       <c r="H1937" s="7"/>
     </row>
     <row r="1938" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1938" s="63"/>
       <c r="H1938" s="7"/>
     </row>
     <row r="1939" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1939" s="63"/>
       <c r="H1939" s="7"/>
     </row>
     <row r="1940" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1940" s="63"/>
       <c r="H1940" s="7"/>
     </row>
     <row r="1941" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1941" s="63"/>
       <c r="H1941" s="7"/>
     </row>
     <row r="1942" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1942" s="63"/>
       <c r="H1942" s="7"/>
     </row>
     <row r="1943" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1943" s="63"/>
       <c r="H1943" s="7"/>
     </row>
     <row r="1944" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1944" s="63"/>
       <c r="H1944" s="7"/>
     </row>
     <row r="1945" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1945" s="63"/>
       <c r="H1945" s="7"/>
     </row>
     <row r="1946" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1946" s="63"/>
       <c r="H1946" s="7"/>
     </row>
     <row r="1947" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1947" s="63"/>
       <c r="H1947" s="7"/>
     </row>
     <row r="1948" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1948" s="63"/>
       <c r="H1948" s="7"/>
     </row>
     <row r="1949" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1949" s="63"/>
       <c r="H1949" s="7"/>
     </row>
     <row r="1950" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1950" s="63"/>
       <c r="H1950" s="7"/>
     </row>
     <row r="1951" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1951" s="63"/>
       <c r="H1951" s="7"/>
     </row>
     <row r="1952" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1952" s="63"/>
       <c r="H1952" s="7"/>
     </row>
     <row r="1953" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1953" s="63"/>
       <c r="H1953" s="7"/>
     </row>
     <row r="1954" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1954" s="63"/>
       <c r="H1954" s="7"/>
     </row>
     <row r="1955" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1955" s="63"/>
       <c r="H1955" s="7"/>
     </row>
     <row r="1956" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1956" s="63"/>
       <c r="H1956" s="7"/>
     </row>
     <row r="1957" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1957" s="63"/>
       <c r="H1957" s="7"/>
     </row>
     <row r="1958" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1958" s="63"/>
       <c r="H1958" s="7"/>
     </row>
     <row r="1959" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1959" s="63"/>
       <c r="H1959" s="7"/>
     </row>
     <row r="1960" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1960" s="63"/>
       <c r="H1960" s="7"/>
     </row>
     <row r="1961" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1961" s="63"/>
       <c r="H1961" s="7"/>
     </row>
     <row r="1962" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1962" s="63"/>
       <c r="H1962" s="7"/>
     </row>
     <row r="1963" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1963" s="63"/>
       <c r="H1963" s="7"/>
     </row>
     <row r="1964" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1964" s="63"/>
       <c r="H1964" s="7"/>
     </row>
     <row r="1965" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1965" s="63"/>
       <c r="H1965" s="7"/>
     </row>
     <row r="1966" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1966" s="63"/>
       <c r="H1966" s="7"/>
     </row>
     <row r="1967" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1967" s="63"/>
       <c r="H1967" s="7"/>
     </row>
     <row r="1968" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1968" s="63"/>
       <c r="H1968" s="7"/>
     </row>
     <row r="1969" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1969" s="63"/>
       <c r="H1969" s="7"/>
     </row>
     <row r="1970" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1970" s="63"/>
       <c r="H1970" s="7"/>
     </row>
     <row r="1971" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1971" s="63"/>
       <c r="H1971" s="7"/>
     </row>
     <row r="1972" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1972" s="63"/>
       <c r="H1972" s="7"/>
     </row>
     <row r="1973" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1973" s="63"/>
       <c r="H1973" s="7"/>
     </row>
     <row r="1974" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1974" s="63"/>
       <c r="H1974" s="7"/>
     </row>
     <row r="1975" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1975" s="63"/>
       <c r="H1975" s="7"/>
     </row>
     <row r="1976" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1976" s="63"/>
       <c r="H1976" s="7"/>
     </row>
     <row r="1977" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1977" s="63"/>
       <c r="H1977" s="7"/>
     </row>
     <row r="1978" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1978" s="63"/>
       <c r="H1978" s="7"/>
     </row>
     <row r="1979" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1979" s="63"/>
       <c r="H1979" s="7"/>
     </row>
     <row r="1980" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1980" s="63"/>
       <c r="H1980" s="7"/>
     </row>
     <row r="1981" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1981" s="63"/>
       <c r="H1981" s="7"/>
     </row>
     <row r="1982" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1982" s="63"/>
       <c r="H1982" s="7"/>
     </row>
     <row r="1983" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1983" s="63"/>
       <c r="H1983" s="7"/>
     </row>
     <row r="1984" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1984" s="63"/>
       <c r="H1984" s="7"/>
     </row>
     <row r="1985" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1985" s="63"/>
       <c r="H1985" s="7"/>
     </row>
     <row r="1986" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1986" s="63"/>
       <c r="H1986" s="7"/>
     </row>
     <row r="1987" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1987" s="63"/>
       <c r="H1987" s="7"/>
     </row>
     <row r="1988" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1988" s="63"/>
       <c r="H1988" s="7"/>
     </row>
     <row r="1989" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1989" s="63"/>
       <c r="H1989" s="7"/>
     </row>
     <row r="1990" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1990" s="63"/>
       <c r="H1990" s="7"/>
     </row>
     <row r="1991" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1991" s="63"/>
       <c r="H1991" s="7"/>
     </row>
     <row r="1992" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1992" s="63"/>
       <c r="H1992" s="7"/>
     </row>
     <row r="1993" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1993" s="63"/>
       <c r="H1993" s="7"/>
     </row>
     <row r="1994" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1994" s="63"/>
       <c r="H1994" s="7"/>
     </row>
     <row r="1995" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1995" s="63"/>
       <c r="H1995" s="7"/>
     </row>
     <row r="1996" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1996" s="63"/>
       <c r="H1996" s="7"/>
     </row>
     <row r="1997" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38262,7 +38784,7 @@
   <mergeCells count="1">
     <mergeCell ref="R6:T6"/>
   </mergeCells>
-  <dataValidations count="16">
+  <dataValidations count="17">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D9:D1609" type="list">
       <formula1>Справочники!$B$2:$B$118</formula1>
       <formula2>0</formula2>
@@ -38299,10 +38821,6 @@
       <formula1>Справочники!$A$2:$A$243</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G7:G1474" type="list">
-      <formula1>Справочники!$H$2:$H$10</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="M7" type="list">
       <formula1>Справочники!$A$2:$A$243</formula1>
       <formula2>0</formula2>
@@ -38325,6 +38843,14 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="lessThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H7:H2686" type="textLength">
       <formula1>100</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G7:G8" type="list">
+      <formula1>Справочники!$H$2:$H$14</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G9:G1996" type="list">
+      <formula1>Справочники!$H$2:$H$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -38474,126 +39000,126 @@
         <v>114</v>
       </c>
       <c r="G4" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I4" s="89" t="s">
         <v>116</v>
-      </c>
-      <c r="I4" s="89" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="D5" s="88" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="E5" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="88" t="s">
+      <c r="F5" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="89" t="s">
         <v>125</v>
-      </c>
-      <c r="I5" s="89" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="86" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="D6" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="E6" s="88" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="F6" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="I6" s="89" t="s">
         <v>134</v>
-      </c>
-      <c r="I6" s="89" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="86" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="87" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="D7" s="88" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="E7" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="E7" s="88" t="s">
+      <c r="F7" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="I7" s="89" t="s">
         <v>143</v>
-      </c>
-      <c r="I7" s="89" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="86" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="87" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="D8" s="88" t="s">
         <v>147</v>
       </c>
-      <c r="D8" s="88" t="s">
+      <c r="E8" s="88" t="s">
         <v>148</v>
       </c>
-      <c r="E8" s="88" t="s">
+      <c r="F8" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>151</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38619,133 +39145,136 @@
         <v>157</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="86" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>160</v>
       </c>
       <c r="C10" s="87" t="s">
         <v>72</v>
       </c>
       <c r="D10" s="88" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="88" t="s">
         <v>161</v>
       </c>
-      <c r="E10" s="88" t="s">
+      <c r="F10" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="H10" s="7" t="s">
         <v>164</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="86" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="87" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>167</v>
       </c>
-      <c r="D11" s="88" t="s">
+      <c r="E11" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="88" t="s">
+      <c r="F11" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="86" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="87" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="D12" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="88" t="s">
+      <c r="E12" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="F12" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="86" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="87" t="s">
         <v>182</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="D13" s="88" t="s">
         <v>183</v>
       </c>
-      <c r="D13" s="88" t="s">
+      <c r="E13" s="88" t="s">
         <v>184</v>
       </c>
-      <c r="E13" s="88" t="s">
+      <c r="F13" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="G13" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="H13" s="7" t="s">
         <v>187</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="86" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="C14" s="87" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="D14" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="E14" s="88" t="s">
         <v>192</v>
       </c>
-      <c r="E14" s="88" t="s">
+      <c r="F14" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="G14" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="H14" s="7" t="s">
         <v>195</v>
       </c>
     </row>
@@ -38769,7 +39298,7 @@
         <v>201</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38792,7 +39321,7 @@
         <v>207</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38815,7 +39344,7 @@
         <v>213</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38861,7 +39390,7 @@
         <v>226</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38884,7 +39413,7 @@
         <v>232</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39183,7 +39712,7 @@
         <v>320</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
